--- a/2022 data/excel_outputs/167_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/167_boothwise_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="591">
   <si>
     <t>Booth No.</t>
   </si>
@@ -73,12 +73,21 @@
     <t>BOOTH 363</t>
   </si>
   <si>
+    <t>BOOTH 363 ROOM NO. 446</t>
+  </si>
+  <si>
+    <t>BOOTH 363 ROOM ROOM NO. 524</t>
+  </si>
+  <si>
     <t>BOOTH 420</t>
   </si>
   <si>
     <t>BOOTH 308</t>
   </si>
   <si>
+    <t>BOOTH 308 ROOM NO. 0</t>
+  </si>
+  <si>
     <t>BOOTH 254</t>
   </si>
   <si>
@@ -100,18 +109,27 @@
     <t>BOOTH 264</t>
   </si>
   <si>
+    <t>BOOTH 264 ROOM NO. 515</t>
+  </si>
+  <si>
     <t>BOOTH 181</t>
   </si>
   <si>
     <t>BOOTH 260</t>
   </si>
   <si>
+    <t>BOOTH 260 ROOM NO. 438</t>
+  </si>
+  <si>
     <t>BOOTH 20</t>
   </si>
   <si>
     <t>BOOTH 262</t>
   </si>
   <si>
+    <t>BOOTH 262 ROOM NO. 482</t>
+  </si>
+  <si>
     <t>BOOTH 121</t>
   </si>
   <si>
@@ -127,6 +145,12 @@
     <t>BOOTH 311</t>
   </si>
   <si>
+    <t>BOOTH 311 ROOM NO. 443</t>
+  </si>
+  <si>
+    <t>BOOTH 311 ROOM ROOM NO. 431</t>
+  </si>
+  <si>
     <t>BOOTH 305</t>
   </si>
   <si>
@@ -172,6 +196,15 @@
     <t>BOOTH 269</t>
   </si>
   <si>
+    <t>BOOTH 269 ROOM NO. 465</t>
+  </si>
+  <si>
+    <t>BOOTH 269 ROOM ROOM NO. 469</t>
+  </si>
+  <si>
+    <t>BOOTH 269 ROOM ROOM ROOM NO. 513</t>
+  </si>
+  <si>
     <t>BOOTH 411</t>
   </si>
   <si>
@@ -190,9 +223,15 @@
     <t>BOOTH 263</t>
   </si>
   <si>
+    <t>BOOTH 263 ROOM NO. 490</t>
+  </si>
+  <si>
     <t>BOOTH 256</t>
   </si>
   <si>
+    <t>BOOTH 256 ROOM NO. 590</t>
+  </si>
+  <si>
     <t>BOOTH 281</t>
   </si>
   <si>
@@ -208,6 +247,9 @@
     <t>BOOTH 178</t>
   </si>
   <si>
+    <t>BOOTH 178 ROOM NO. 433</t>
+  </si>
+  <si>
     <t>BOOTH 360</t>
   </si>
   <si>
@@ -271,6 +313,12 @@
     <t>BOOTH 234</t>
   </si>
   <si>
+    <t>BOOTH 234 ROOM NO. 519</t>
+  </si>
+  <si>
+    <t>BOOTH 234 ROOM ROOM NO. 589</t>
+  </si>
+  <si>
     <t>BOOTH 315</t>
   </si>
   <si>
@@ -298,6 +346,9 @@
     <t>BOOTH 239</t>
   </si>
   <si>
+    <t>BOOTH 243 ROOM NO. 431</t>
+  </si>
+  <si>
     <t>BOOTH 318</t>
   </si>
   <si>
@@ -358,6 +409,12 @@
     <t>BOOTH 165</t>
   </si>
   <si>
+    <t>BOOTH 333 ROOM NO. 510</t>
+  </si>
+  <si>
+    <t>BOOTH 333 ROOM ROOM NO. 465</t>
+  </si>
+  <si>
     <t>BOOTH 374</t>
   </si>
   <si>
@@ -367,6 +424,9 @@
     <t>BOOTH 226</t>
   </si>
   <si>
+    <t>BOOTH 226 ROOM NO. 500</t>
+  </si>
+  <si>
     <t>BOOTH 355</t>
   </si>
   <si>
@@ -400,6 +460,9 @@
     <t>BOOTH 323</t>
   </si>
   <si>
+    <t>BOOTH 323 ROOM NO. 426</t>
+  </si>
+  <si>
     <t>BOOTH 417</t>
   </si>
   <si>
@@ -424,6 +487,12 @@
     <t>BOOTH 338</t>
   </si>
   <si>
+    <t>BOOTH 338 ROOM NO. 514</t>
+  </si>
+  <si>
+    <t>BOOTH 383 ROOM NO. 449</t>
+  </si>
+  <si>
     <t>BOOTH 388</t>
   </si>
   <si>
@@ -436,6 +505,9 @@
     <t>BOOTH 376</t>
   </si>
   <si>
+    <t>BOOTH 227 ROOM NO. 477</t>
+  </si>
+  <si>
     <t>BOOTH 247</t>
   </si>
   <si>
@@ -445,12 +517,21 @@
     <t>BOOTH 330</t>
   </si>
   <si>
+    <t>BOOTH 330 ROOM NO. 497</t>
+  </si>
+  <si>
     <t>BOOTH 272</t>
   </si>
   <si>
     <t>BOOTH 403</t>
   </si>
   <si>
+    <t>BOOTH 403 ROOM NO. 501</t>
+  </si>
+  <si>
+    <t>BOOTH 403 ROOM ROOM NO. 492</t>
+  </si>
+  <si>
     <t>BOOTH 19</t>
   </si>
   <si>
@@ -469,6 +550,9 @@
     <t>BOOTH 358</t>
   </si>
   <si>
+    <t>BOOTH 254 ROOM NO. 569</t>
+  </si>
+  <si>
     <t>BOOTH 217</t>
   </si>
   <si>
@@ -478,6 +562,9 @@
     <t>BOOTH 34</t>
   </si>
   <si>
+    <t>BOOTH 39 ROOM NO. 485</t>
+  </si>
+  <si>
     <t>BOOTH 328</t>
   </si>
   <si>
@@ -511,6 +598,9 @@
     <t>BOOTH 176</t>
   </si>
   <si>
+    <t>BOOTH 328 ROOM NO. 0</t>
+  </si>
+  <si>
     <t>BOOTH 317</t>
   </si>
   <si>
@@ -523,12 +613,18 @@
     <t>BOOTH 50</t>
   </si>
   <si>
+    <t>BOOTH 50 ROOM NO. 504</t>
+  </si>
+  <si>
     <t>BOOTH 396</t>
   </si>
   <si>
     <t>BOOTH 406</t>
   </si>
   <si>
+    <t>BOOTH 406 ROOM NO. 441</t>
+  </si>
+  <si>
     <t>BOOTH 381</t>
   </si>
   <si>
@@ -544,6 +640,9 @@
     <t>BOOTH 295</t>
   </si>
   <si>
+    <t>BOOTH 295 ROOM NO. 433</t>
+  </si>
+  <si>
     <t>BOOTH 224</t>
   </si>
   <si>
@@ -580,6 +679,9 @@
     <t>BOOTH 125</t>
   </si>
   <si>
+    <t>BOOTH 125 ROOM NO. 449</t>
+  </si>
+  <si>
     <t>BOOTH 395</t>
   </si>
   <si>
@@ -604,6 +706,9 @@
     <t>BOOTH 190</t>
   </si>
   <si>
+    <t>BOOTH 190 ROOM NO. 524</t>
+  </si>
+  <si>
     <t>BOOTH 270</t>
   </si>
   <si>
@@ -619,9 +724,15 @@
     <t>BOOTH 126</t>
   </si>
   <si>
+    <t>BOOTH 126 ROOM NO. 464</t>
+  </si>
+  <si>
     <t>BOOTH 306</t>
   </si>
   <si>
+    <t>BOOTH 364 ROOM NO. 512</t>
+  </si>
+  <si>
     <t>BOOTH 416</t>
   </si>
   <si>
@@ -643,6 +754,9 @@
     <t>BOOTH 413</t>
   </si>
   <si>
+    <t>BOOTH 413 ROOM NO. 456</t>
+  </si>
+  <si>
     <t>BOOTH 248</t>
   </si>
   <si>
@@ -673,6 +787,9 @@
     <t>BOOTH 198</t>
   </si>
   <si>
+    <t>BOOTH 198 ROOM NO. 467</t>
+  </si>
+  <si>
     <t>BOOTH 274</t>
   </si>
   <si>
@@ -709,6 +826,9 @@
     <t>BOOTH 271</t>
   </si>
   <si>
+    <t>BOOTH 257 ROOM NO. 522</t>
+  </si>
+  <si>
     <t>BOOTH 382</t>
   </si>
   <si>
@@ -757,6 +877,9 @@
     <t>BOOTH 232</t>
   </si>
   <si>
+    <t>BOOTH 404 ROOM NO. 454</t>
+  </si>
+  <si>
     <t>BOOTH 208</t>
   </si>
   <si>
@@ -766,6 +889,9 @@
     <t>BOOTH 366</t>
   </si>
   <si>
+    <t>BOOTH 366 ROOM NO. 441</t>
+  </si>
+  <si>
     <t>BOOTH 346</t>
   </si>
   <si>
@@ -781,6 +907,9 @@
     <t>BOOTH 290</t>
   </si>
   <si>
+    <t>BOOTH 317 ROOM NO. 454</t>
+  </si>
+  <si>
     <t>BOOTH 414</t>
   </si>
   <si>
@@ -790,6 +919,9 @@
     <t>BOOTH 163</t>
   </si>
   <si>
+    <t>BOOTH 288 ROOM NO. 446</t>
+  </si>
+  <si>
     <t>BOOTH 325</t>
   </si>
   <si>
@@ -805,6 +937,9 @@
     <t>BOOTH 393</t>
   </si>
   <si>
+    <t>BOOTH 367 ROOM NO. 455</t>
+  </si>
+  <si>
     <t>BOOTH 149</t>
   </si>
   <si>
@@ -814,10 +949,844 @@
     <t>BOOTH 110</t>
   </si>
   <si>
+    <t>BOOTH 110 ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 110 ROOM ROOM NO. 0</t>
+  </si>
+  <si>
     <t>BOOTH 386</t>
   </si>
   <si>
+    <t>BOOTH 386 ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 0</t>
+  </si>
+  <si>
+    <t>BOOTH 386 ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 133687</t>
+  </si>
+  <si>
     <t>BOOTH 140</t>
+  </si>
+  <si>
+    <t>BOOTH 140 ROOM NO. 133827</t>
   </si>
 </sst>
 </file>
@@ -1341,6 +2310,9 @@
       <c r="A4">
         <v>446</v>
       </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
       <c r="C4">
         <v>257</v>
       </c>
@@ -1391,6 +2363,9 @@
       <c r="A5">
         <v>524</v>
       </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
       <c r="C5">
         <v>148</v>
       </c>
@@ -1442,7 +2417,7 @@
         <v>420</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>135</v>
@@ -1495,7 +2470,7 @@
         <v>308</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>180</v>
@@ -1546,6 +2521,9 @@
     <row r="8" spans="1:18">
       <c r="A8">
         <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1598,7 +2576,7 @@
         <v>254</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>131</v>
@@ -1651,7 +2629,7 @@
         <v>235</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>308</v>
@@ -1704,7 +2682,7 @@
         <v>227</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>351</v>
@@ -1757,7 +2735,7 @@
         <v>236</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>121</v>
@@ -1810,7 +2788,7 @@
         <v>293</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>306</v>
@@ -1863,7 +2841,7 @@
         <v>211</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>254</v>
@@ -1916,7 +2894,7 @@
         <v>264</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>392</v>
@@ -1968,6 +2946,9 @@
       <c r="A16">
         <v>515</v>
       </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
       <c r="C16">
         <v>135</v>
       </c>
@@ -2019,7 +3000,7 @@
         <v>181</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>370</v>
@@ -2072,7 +3053,7 @@
         <v>260</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>313</v>
@@ -2124,6 +3105,9 @@
       <c r="A19">
         <v>438</v>
       </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
       <c r="C19">
         <v>152</v>
       </c>
@@ -2175,7 +3159,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>212</v>
@@ -2228,7 +3212,7 @@
         <v>262</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>382</v>
@@ -2280,6 +3264,9 @@
       <c r="A22">
         <v>482</v>
       </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
       <c r="C22">
         <v>107</v>
       </c>
@@ -2331,7 +3318,7 @@
         <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C23">
         <v>151</v>
@@ -2384,7 +3371,7 @@
         <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>330</v>
@@ -2437,7 +3424,7 @@
         <v>238</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C25">
         <v>86</v>
@@ -2490,7 +3477,7 @@
         <v>235</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C26">
         <v>119</v>
@@ -2543,7 +3530,7 @@
         <v>379</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C27">
         <v>207</v>
@@ -2596,7 +3583,7 @@
         <v>227</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C28">
         <v>449</v>
@@ -2649,7 +3636,7 @@
         <v>311</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C29">
         <v>324</v>
@@ -2701,6 +3688,9 @@
       <c r="A30">
         <v>443</v>
       </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
       <c r="C30">
         <v>105</v>
       </c>
@@ -2751,6 +3741,9 @@
       <c r="A31">
         <v>431</v>
       </c>
+      <c r="B31" t="s">
+        <v>44</v>
+      </c>
       <c r="C31">
         <v>186</v>
       </c>
@@ -2802,7 +3795,7 @@
         <v>305</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C32">
         <v>148</v>
@@ -2855,7 +3848,7 @@
         <v>246</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C33">
         <v>127</v>
@@ -2908,7 +3901,7 @@
         <v>356</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C34">
         <v>120</v>
@@ -2961,7 +3954,7 @@
         <v>244</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C35">
         <v>354</v>
@@ -3014,7 +4007,7 @@
         <v>302</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C36">
         <v>224</v>
@@ -3067,7 +4060,7 @@
         <v>240</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C37">
         <v>191</v>
@@ -3120,7 +4113,7 @@
         <v>273</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C38">
         <v>193</v>
@@ -3173,7 +4166,7 @@
         <v>289</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C39">
         <v>183</v>
@@ -3226,7 +4219,7 @@
         <v>313</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C40">
         <v>427</v>
@@ -3279,7 +4272,7 @@
         <v>273</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C41">
         <v>119</v>
@@ -3332,7 +4325,7 @@
         <v>202</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C42">
         <v>437</v>
@@ -3385,7 +4378,7 @@
         <v>260</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C43">
         <v>346</v>
@@ -3438,7 +4431,7 @@
         <v>181</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C44">
         <v>288</v>
@@ -3491,7 +4484,7 @@
         <v>185</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C45">
         <v>358</v>
@@ -3544,7 +4537,7 @@
         <v>222</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C46">
         <v>176</v>
@@ -3597,7 +4590,7 @@
         <v>206</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C47">
         <v>262</v>
@@ -3650,7 +4643,7 @@
         <v>225</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C48">
         <v>146</v>
@@ -3703,7 +4696,7 @@
         <v>269</v>
       </c>
       <c r="B49" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C49">
         <v>140</v>
@@ -3755,6 +4748,9 @@
       <c r="A50">
         <v>465</v>
       </c>
+      <c r="B50" t="s">
+        <v>60</v>
+      </c>
       <c r="C50">
         <v>211</v>
       </c>
@@ -3805,6 +4801,9 @@
       <c r="A51">
         <v>469</v>
       </c>
+      <c r="B51" t="s">
+        <v>61</v>
+      </c>
       <c r="C51">
         <v>73</v>
       </c>
@@ -3855,6 +4854,9 @@
       <c r="A52">
         <v>513</v>
       </c>
+      <c r="B52" t="s">
+        <v>62</v>
+      </c>
       <c r="C52">
         <v>209</v>
       </c>
@@ -3906,7 +4908,7 @@
         <v>411</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C53">
         <v>219</v>
@@ -3959,7 +4961,7 @@
         <v>265</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C54">
         <v>216</v>
@@ -4012,7 +5014,7 @@
         <v>333</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C55">
         <v>147</v>
@@ -4065,7 +5067,7 @@
         <v>350</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C56">
         <v>151</v>
@@ -4118,7 +5120,7 @@
         <v>340</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C57">
         <v>121</v>
@@ -4171,7 +5173,7 @@
         <v>263</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C58">
         <v>102</v>
@@ -4223,6 +5225,9 @@
       <c r="A59">
         <v>490</v>
       </c>
+      <c r="B59" t="s">
+        <v>69</v>
+      </c>
       <c r="C59">
         <v>310</v>
       </c>
@@ -4274,7 +5279,7 @@
         <v>256</v>
       </c>
       <c r="B60" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C60">
         <v>430</v>
@@ -4326,6 +5331,9 @@
       <c r="A61">
         <v>590</v>
       </c>
+      <c r="B61" t="s">
+        <v>71</v>
+      </c>
       <c r="C61">
         <v>143</v>
       </c>
@@ -4377,7 +5385,7 @@
         <v>273</v>
       </c>
       <c r="B62" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C62">
         <v>268</v>
@@ -4430,7 +5438,7 @@
         <v>281</v>
       </c>
       <c r="B63" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C63">
         <v>209</v>
@@ -4483,7 +5491,7 @@
         <v>341</v>
       </c>
       <c r="B64" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C64">
         <v>202</v>
@@ -4536,7 +5544,7 @@
         <v>324</v>
       </c>
       <c r="B65" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C65">
         <v>195</v>
@@ -4589,7 +5597,7 @@
         <v>253</v>
       </c>
       <c r="B66" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C66">
         <v>243</v>
@@ -4642,7 +5650,7 @@
         <v>178</v>
       </c>
       <c r="B67" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C67">
         <v>212</v>
@@ -4694,6 +5702,9 @@
       <c r="A68">
         <v>433</v>
       </c>
+      <c r="B68" t="s">
+        <v>77</v>
+      </c>
       <c r="C68">
         <v>102</v>
       </c>
@@ -4745,7 +5756,7 @@
         <v>360</v>
       </c>
       <c r="B69" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C69">
         <v>195</v>
@@ -4798,7 +5809,7 @@
         <v>267</v>
       </c>
       <c r="B70" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C70">
         <v>132</v>
@@ -4851,7 +5862,7 @@
         <v>275</v>
       </c>
       <c r="B71" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C71">
         <v>51</v>
@@ -4904,7 +5915,7 @@
         <v>309</v>
       </c>
       <c r="B72" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C72">
         <v>189</v>
@@ -4957,7 +5968,7 @@
         <v>122</v>
       </c>
       <c r="B73" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C73">
         <v>60</v>
@@ -5010,7 +6021,7 @@
         <v>181</v>
       </c>
       <c r="B74" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C74">
         <v>277</v>
@@ -5063,7 +6074,7 @@
         <v>243</v>
       </c>
       <c r="B75" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C75">
         <v>172</v>
@@ -5116,7 +6127,7 @@
         <v>255</v>
       </c>
       <c r="B76" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C76">
         <v>147</v>
@@ -5169,7 +6180,7 @@
         <v>375</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C77">
         <v>166</v>
@@ -5222,7 +6233,7 @@
         <v>339</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C78">
         <v>141</v>
@@ -5275,7 +6286,7 @@
         <v>199</v>
       </c>
       <c r="B79" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C79">
         <v>210</v>
@@ -5328,7 +6339,7 @@
         <v>250</v>
       </c>
       <c r="B80" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C80">
         <v>273</v>
@@ -5381,7 +6392,7 @@
         <v>241</v>
       </c>
       <c r="B81" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C81">
         <v>284</v>
@@ -5434,7 +6445,7 @@
         <v>390</v>
       </c>
       <c r="B82" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C82">
         <v>263</v>
@@ -5487,7 +6498,7 @@
         <v>337</v>
       </c>
       <c r="B83" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C83">
         <v>201</v>
@@ -5540,7 +6551,7 @@
         <v>299</v>
       </c>
       <c r="B84" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C84">
         <v>79</v>
@@ -5593,7 +6604,7 @@
         <v>324</v>
       </c>
       <c r="B85" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C85">
         <v>100</v>
@@ -5646,7 +6657,7 @@
         <v>278</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C86">
         <v>190</v>
@@ -5699,7 +6710,7 @@
         <v>166</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C87">
         <v>275</v>
@@ -5752,7 +6763,7 @@
         <v>257</v>
       </c>
       <c r="B88" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C88">
         <v>86</v>
@@ -5805,7 +6816,7 @@
         <v>359</v>
       </c>
       <c r="B89" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C89">
         <v>207</v>
@@ -5858,7 +6869,7 @@
         <v>264</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C90">
         <v>203</v>
@@ -5911,7 +6922,7 @@
         <v>383</v>
       </c>
       <c r="B91" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C91">
         <v>236</v>
@@ -5964,7 +6975,7 @@
         <v>234</v>
       </c>
       <c r="B92" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C92">
         <v>210</v>
@@ -6016,6 +7027,9 @@
       <c r="A93">
         <v>519</v>
       </c>
+      <c r="B93" t="s">
+        <v>99</v>
+      </c>
       <c r="C93">
         <v>311</v>
       </c>
@@ -6066,6 +7080,9 @@
       <c r="A94">
         <v>589</v>
       </c>
+      <c r="B94" t="s">
+        <v>100</v>
+      </c>
       <c r="C94">
         <v>214</v>
       </c>
@@ -6117,7 +7134,7 @@
         <v>315</v>
       </c>
       <c r="B95" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="C95">
         <v>176</v>
@@ -6170,7 +7187,7 @@
         <v>207</v>
       </c>
       <c r="B96" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C96">
         <v>51</v>
@@ -6223,7 +7240,7 @@
         <v>216</v>
       </c>
       <c r="B97" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C97">
         <v>167</v>
@@ -6276,7 +7293,7 @@
         <v>340</v>
       </c>
       <c r="B98" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C98">
         <v>185</v>
@@ -6329,7 +7346,7 @@
         <v>423</v>
       </c>
       <c r="B99" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="C99">
         <v>224</v>
@@ -6382,7 +7399,7 @@
         <v>283</v>
       </c>
       <c r="B100" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C100">
         <v>158</v>
@@ -6435,7 +7452,7 @@
         <v>342</v>
       </c>
       <c r="B101" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C101">
         <v>277</v>
@@ -6488,7 +7505,7 @@
         <v>349</v>
       </c>
       <c r="B102" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C102">
         <v>262</v>
@@ -6541,7 +7558,7 @@
         <v>332</v>
       </c>
       <c r="B103" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C103">
         <v>187</v>
@@ -6594,7 +7611,7 @@
         <v>283</v>
       </c>
       <c r="B104" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="C104">
         <v>81</v>
@@ -6647,7 +7664,7 @@
         <v>239</v>
       </c>
       <c r="B105" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C105">
         <v>161</v>
@@ -6700,7 +7717,7 @@
         <v>243</v>
       </c>
       <c r="B106" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C106">
         <v>145</v>
@@ -6752,6 +7769,9 @@
       <c r="A107">
         <v>431</v>
       </c>
+      <c r="B107" t="s">
+        <v>110</v>
+      </c>
       <c r="C107">
         <v>211</v>
       </c>
@@ -6803,7 +7823,7 @@
         <v>313</v>
       </c>
       <c r="B108" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C108">
         <v>209</v>
@@ -6856,7 +7876,7 @@
         <v>318</v>
       </c>
       <c r="B109" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C109">
         <v>84</v>
@@ -6909,7 +7929,7 @@
         <v>102</v>
       </c>
       <c r="B110" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C110">
         <v>347</v>
@@ -6962,7 +7982,7 @@
         <v>311</v>
       </c>
       <c r="B111" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C111">
         <v>99</v>
@@ -7015,7 +8035,7 @@
         <v>114</v>
       </c>
       <c r="B112" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="C112">
         <v>62</v>
@@ -7068,7 +8088,7 @@
         <v>105</v>
       </c>
       <c r="B113" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="C113">
         <v>177</v>
@@ -7121,7 +8141,7 @@
         <v>85</v>
       </c>
       <c r="B114" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C114">
         <v>68</v>
@@ -7174,7 +8194,7 @@
         <v>133</v>
       </c>
       <c r="B115" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C115">
         <v>236</v>
@@ -7227,7 +8247,7 @@
         <v>210</v>
       </c>
       <c r="B116" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C116">
         <v>315</v>
@@ -7280,7 +8300,7 @@
         <v>334</v>
       </c>
       <c r="B117" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C117">
         <v>203</v>
@@ -7333,7 +8353,7 @@
         <v>265</v>
       </c>
       <c r="B118" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C118">
         <v>250</v>
@@ -7386,7 +8406,7 @@
         <v>201</v>
       </c>
       <c r="B119" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="C119">
         <v>166</v>
@@ -7439,7 +8459,7 @@
         <v>145</v>
       </c>
       <c r="B120" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="C120">
         <v>123</v>
@@ -7492,7 +8512,7 @@
         <v>253</v>
       </c>
       <c r="B121" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C121">
         <v>208</v>
@@ -7545,7 +8565,7 @@
         <v>171</v>
       </c>
       <c r="B122" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="C122">
         <v>33</v>
@@ -7598,7 +8618,7 @@
         <v>288</v>
       </c>
       <c r="B123" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C123">
         <v>269</v>
@@ -7651,7 +8671,7 @@
         <v>249</v>
       </c>
       <c r="B124" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C124">
         <v>323</v>
@@ -7704,7 +8724,7 @@
         <v>188</v>
       </c>
       <c r="B125" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C125">
         <v>299</v>
@@ -7757,7 +8777,7 @@
         <v>287</v>
       </c>
       <c r="B126" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C126">
         <v>258</v>
@@ -7810,7 +8830,7 @@
         <v>260</v>
       </c>
       <c r="B127" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C127">
         <v>138</v>
@@ -7863,7 +8883,7 @@
         <v>183</v>
       </c>
       <c r="B128" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C128">
         <v>158</v>
@@ -7916,7 +8936,7 @@
         <v>298</v>
       </c>
       <c r="B129" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="C129">
         <v>303</v>
@@ -7969,7 +8989,7 @@
         <v>329</v>
       </c>
       <c r="B130" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C130">
         <v>147</v>
@@ -8022,7 +9042,7 @@
         <v>215</v>
       </c>
       <c r="B131" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C131">
         <v>106</v>
@@ -8075,7 +9095,7 @@
         <v>165</v>
       </c>
       <c r="B132" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="C132">
         <v>74</v>
@@ -8128,7 +9148,7 @@
         <v>333</v>
       </c>
       <c r="B133" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C133">
         <v>115</v>
@@ -8180,6 +9200,9 @@
       <c r="A134">
         <v>510</v>
       </c>
+      <c r="B134" t="s">
+        <v>131</v>
+      </c>
       <c r="C134">
         <v>221</v>
       </c>
@@ -8230,6 +9253,9 @@
       <c r="A135">
         <v>465</v>
       </c>
+      <c r="B135" t="s">
+        <v>132</v>
+      </c>
       <c r="C135">
         <v>206</v>
       </c>
@@ -8281,7 +9307,7 @@
         <v>374</v>
       </c>
       <c r="B136" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="C136">
         <v>132</v>
@@ -8334,7 +9360,7 @@
         <v>245</v>
       </c>
       <c r="B137" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="C137">
         <v>204</v>
@@ -8387,7 +9413,7 @@
         <v>243</v>
       </c>
       <c r="B138" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C138">
         <v>72</v>
@@ -8440,7 +9466,7 @@
         <v>340</v>
       </c>
       <c r="B139" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C139">
         <v>85</v>
@@ -8493,7 +9519,7 @@
         <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C140">
         <v>158</v>
@@ -8546,7 +9572,7 @@
         <v>226</v>
       </c>
       <c r="B141" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C141">
         <v>121</v>
@@ -8598,6 +9624,9 @@
       <c r="A142">
         <v>500</v>
       </c>
+      <c r="B142" t="s">
+        <v>136</v>
+      </c>
       <c r="C142">
         <v>85</v>
       </c>
@@ -8649,7 +9678,7 @@
         <v>355</v>
       </c>
       <c r="B143" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C143">
         <v>152</v>
@@ -8702,7 +9731,7 @@
         <v>156</v>
       </c>
       <c r="B144" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C144">
         <v>156</v>
@@ -8755,7 +9784,7 @@
         <v>214</v>
       </c>
       <c r="B145" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="C145">
         <v>218</v>
@@ -8808,7 +9837,7 @@
         <v>307</v>
       </c>
       <c r="B146" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C146">
         <v>226</v>
@@ -8861,7 +9890,7 @@
         <v>314</v>
       </c>
       <c r="B147" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C147">
         <v>290</v>
@@ -8914,7 +9943,7 @@
         <v>117</v>
       </c>
       <c r="B148" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="C148">
         <v>200</v>
@@ -8967,7 +9996,7 @@
         <v>210</v>
       </c>
       <c r="B149" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C149">
         <v>116</v>
@@ -9020,7 +10049,7 @@
         <v>188</v>
       </c>
       <c r="B150" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C150">
         <v>193</v>
@@ -9073,7 +10102,7 @@
         <v>281</v>
       </c>
       <c r="B151" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C151">
         <v>165</v>
@@ -9126,7 +10155,7 @@
         <v>201</v>
       </c>
       <c r="B152" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="C152">
         <v>37</v>
@@ -9179,7 +10208,7 @@
         <v>423</v>
       </c>
       <c r="B153" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="C153">
         <v>129</v>
@@ -9232,7 +10261,7 @@
         <v>336</v>
       </c>
       <c r="B154" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C154">
         <v>156</v>
@@ -9285,7 +10314,7 @@
         <v>297</v>
       </c>
       <c r="B155" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="C155">
         <v>83</v>
@@ -9338,7 +10367,7 @@
         <v>357</v>
       </c>
       <c r="B156" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="C156">
         <v>121</v>
@@ -9391,7 +10420,7 @@
         <v>82</v>
       </c>
       <c r="B157" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="C157">
         <v>226</v>
@@ -9444,7 +10473,7 @@
         <v>210</v>
       </c>
       <c r="B158" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C158">
         <v>455</v>
@@ -9497,7 +10526,7 @@
         <v>349</v>
       </c>
       <c r="B159" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="C159">
         <v>301</v>
@@ -9550,7 +10579,7 @@
         <v>323</v>
       </c>
       <c r="B160" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="C160">
         <v>204</v>
@@ -9602,6 +10631,9 @@
       <c r="A161">
         <v>426</v>
       </c>
+      <c r="B161" t="s">
+        <v>148</v>
+      </c>
       <c r="C161">
         <v>199</v>
       </c>
@@ -9653,7 +10685,7 @@
         <v>417</v>
       </c>
       <c r="B162" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="C162">
         <v>296</v>
@@ -9706,7 +10738,7 @@
         <v>364</v>
       </c>
       <c r="B163" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="C163">
         <v>179</v>
@@ -9759,7 +10791,7 @@
         <v>294</v>
       </c>
       <c r="B164" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C164">
         <v>186</v>
@@ -9812,7 +10844,7 @@
         <v>161</v>
       </c>
       <c r="B165" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C165">
         <v>283</v>
@@ -9865,7 +10897,7 @@
         <v>203</v>
       </c>
       <c r="B166" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="C166">
         <v>250</v>
@@ -9918,7 +10950,7 @@
         <v>279</v>
       </c>
       <c r="B167" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C167">
         <v>200</v>
@@ -9971,7 +11003,7 @@
         <v>231</v>
       </c>
       <c r="B168" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C168">
         <v>213</v>
@@ -10024,7 +11056,7 @@
         <v>329</v>
       </c>
       <c r="B169" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C169">
         <v>102</v>
@@ -10077,7 +11109,7 @@
         <v>338</v>
       </c>
       <c r="B170" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="C170">
         <v>211</v>
@@ -10129,6 +11161,9 @@
       <c r="A171">
         <v>514</v>
       </c>
+      <c r="B171" t="s">
+        <v>157</v>
+      </c>
       <c r="C171">
         <v>104</v>
       </c>
@@ -10180,7 +11215,7 @@
         <v>383</v>
       </c>
       <c r="B172" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C172">
         <v>146</v>
@@ -10232,6 +11267,9 @@
       <c r="A173">
         <v>449</v>
       </c>
+      <c r="B173" t="s">
+        <v>158</v>
+      </c>
       <c r="C173">
         <v>276</v>
       </c>
@@ -10283,7 +11321,7 @@
         <v>388</v>
       </c>
       <c r="B174" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="C174">
         <v>231</v>
@@ -10336,7 +11374,7 @@
         <v>303</v>
       </c>
       <c r="B175" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C175">
         <v>208</v>
@@ -10389,7 +11427,7 @@
         <v>352</v>
       </c>
       <c r="B176" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="C176">
         <v>291</v>
@@ -10442,7 +11480,7 @@
         <v>390</v>
       </c>
       <c r="B177" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C177">
         <v>203</v>
@@ -10495,7 +11533,7 @@
         <v>376</v>
       </c>
       <c r="B178" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="C178">
         <v>193</v>
@@ -10548,7 +11586,7 @@
         <v>289</v>
       </c>
       <c r="B179" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C179">
         <v>308</v>
@@ -10601,7 +11639,7 @@
         <v>239</v>
       </c>
       <c r="B180" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C180">
         <v>194</v>
@@ -10654,7 +11692,7 @@
         <v>227</v>
       </c>
       <c r="B181" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C181">
         <v>298</v>
@@ -10706,6 +11744,9 @@
       <c r="A182">
         <v>477</v>
       </c>
+      <c r="B182" t="s">
+        <v>163</v>
+      </c>
       <c r="C182">
         <v>198</v>
       </c>
@@ -10757,7 +11798,7 @@
         <v>247</v>
       </c>
       <c r="B183" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="C183">
         <v>270</v>
@@ -10810,7 +11851,7 @@
         <v>63</v>
       </c>
       <c r="B184" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C184">
         <v>291</v>
@@ -10863,7 +11904,7 @@
         <v>256</v>
       </c>
       <c r="B185" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C185">
         <v>21</v>
@@ -10916,7 +11957,7 @@
         <v>367</v>
       </c>
       <c r="B186" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="C186">
         <v>135</v>
@@ -10969,7 +12010,7 @@
         <v>330</v>
       </c>
       <c r="B187" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="C187">
         <v>94</v>
@@ -11021,6 +12062,9 @@
       <c r="A188">
         <v>497</v>
       </c>
+      <c r="B188" t="s">
+        <v>167</v>
+      </c>
       <c r="C188">
         <v>124</v>
       </c>
@@ -11072,7 +12116,7 @@
         <v>272</v>
       </c>
       <c r="B189" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="C189">
         <v>96</v>
@@ -11125,7 +12169,7 @@
         <v>260</v>
       </c>
       <c r="B190" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C190">
         <v>112</v>
@@ -11178,7 +12222,7 @@
         <v>403</v>
       </c>
       <c r="B191" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="C191">
         <v>167</v>
@@ -11230,6 +12274,9 @@
       <c r="A192">
         <v>501</v>
       </c>
+      <c r="B192" t="s">
+        <v>170</v>
+      </c>
       <c r="C192">
         <v>155</v>
       </c>
@@ -11280,6 +12327,9 @@
       <c r="A193">
         <v>492</v>
       </c>
+      <c r="B193" t="s">
+        <v>171</v>
+      </c>
       <c r="C193">
         <v>110</v>
       </c>
@@ -11331,7 +12381,7 @@
         <v>281</v>
       </c>
       <c r="B194" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C194">
         <v>287</v>
@@ -11384,7 +12434,7 @@
         <v>19</v>
       </c>
       <c r="B195" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="C195">
         <v>396</v>
@@ -11437,7 +12487,7 @@
         <v>287</v>
       </c>
       <c r="B196" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C196">
         <v>282</v>
@@ -11490,7 +12540,7 @@
         <v>215</v>
       </c>
       <c r="B197" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C197">
         <v>294</v>
@@ -11543,7 +12593,7 @@
         <v>39</v>
       </c>
       <c r="B198" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="C198">
         <v>344</v>
@@ -11596,7 +12646,7 @@
         <v>415</v>
       </c>
       <c r="B199" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="C199">
         <v>210</v>
@@ -11649,7 +12699,7 @@
         <v>104</v>
       </c>
       <c r="B200" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="C200">
         <v>393</v>
@@ -11702,7 +12752,7 @@
         <v>408</v>
       </c>
       <c r="B201" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="C201">
         <v>169</v>
@@ -11755,7 +12805,7 @@
         <v>358</v>
       </c>
       <c r="B202" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="C202">
         <v>234</v>
@@ -11808,7 +12858,7 @@
         <v>337</v>
       </c>
       <c r="B203" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C203">
         <v>307</v>
@@ -11861,7 +12911,7 @@
         <v>254</v>
       </c>
       <c r="B204" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C204">
         <v>360</v>
@@ -11913,6 +12963,9 @@
       <c r="A205">
         <v>569</v>
       </c>
+      <c r="B205" t="s">
+        <v>178</v>
+      </c>
       <c r="C205">
         <v>144</v>
       </c>
@@ -11964,7 +13017,7 @@
         <v>359</v>
       </c>
       <c r="B206" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C206">
         <v>202</v>
@@ -12017,7 +13070,7 @@
         <v>217</v>
       </c>
       <c r="B207" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="C207">
         <v>285</v>
@@ -12070,7 +13123,7 @@
         <v>13</v>
       </c>
       <c r="B208" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="C208">
         <v>401</v>
@@ -12123,7 +13176,7 @@
         <v>34</v>
       </c>
       <c r="B209" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="C209">
         <v>456</v>
@@ -12176,7 +13229,7 @@
         <v>39</v>
       </c>
       <c r="B210" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="C210">
         <v>305</v>
@@ -12228,6 +13281,9 @@
       <c r="A211">
         <v>485</v>
       </c>
+      <c r="B211" t="s">
+        <v>182</v>
+      </c>
       <c r="C211">
         <v>116</v>
       </c>
@@ -12279,7 +13335,7 @@
         <v>216</v>
       </c>
       <c r="B212" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C212">
         <v>178</v>
@@ -12332,7 +13388,7 @@
         <v>328</v>
       </c>
       <c r="B213" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="C213">
         <v>115</v>
@@ -12385,7 +13441,7 @@
         <v>264</v>
       </c>
       <c r="B214" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C214">
         <v>182</v>
@@ -12438,7 +13494,7 @@
         <v>229</v>
       </c>
       <c r="B215" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="C215">
         <v>75</v>
@@ -12491,7 +13547,7 @@
         <v>303</v>
       </c>
       <c r="B216" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="C216">
         <v>249</v>
@@ -12544,7 +13600,7 @@
         <v>253</v>
       </c>
       <c r="B217" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C217">
         <v>154</v>
@@ -12597,7 +13653,7 @@
         <v>320</v>
       </c>
       <c r="B218" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="C218">
         <v>199</v>
@@ -12650,7 +13706,7 @@
         <v>143</v>
       </c>
       <c r="B219" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="C219">
         <v>241</v>
@@ -12703,7 +13759,7 @@
         <v>183</v>
       </c>
       <c r="B220" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C220">
         <v>415</v>
@@ -12756,7 +13812,7 @@
         <v>316</v>
       </c>
       <c r="B221" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="C221">
         <v>341</v>
@@ -12809,7 +13865,7 @@
         <v>243</v>
       </c>
       <c r="B222" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C222">
         <v>187</v>
@@ -12862,7 +13918,7 @@
         <v>411</v>
       </c>
       <c r="B223" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C223">
         <v>155</v>
@@ -12915,7 +13971,7 @@
         <v>246</v>
       </c>
       <c r="B224" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C224">
         <v>84</v>
@@ -12968,7 +14024,7 @@
         <v>220</v>
       </c>
       <c r="B225" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="C225">
         <v>126</v>
@@ -13021,7 +14077,7 @@
         <v>98</v>
       </c>
       <c r="B226" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="C226">
         <v>389</v>
@@ -13074,7 +14130,7 @@
         <v>196</v>
       </c>
       <c r="B227" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="C227">
         <v>401</v>
@@ -13127,7 +14183,7 @@
         <v>280</v>
       </c>
       <c r="B228" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="C228">
         <v>180</v>
@@ -13180,7 +14236,7 @@
         <v>354</v>
       </c>
       <c r="B229" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="C229">
         <v>258</v>
@@ -13233,7 +14289,7 @@
         <v>216</v>
       </c>
       <c r="B230" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C230">
         <v>263</v>
@@ -13286,7 +14342,7 @@
         <v>313</v>
       </c>
       <c r="B231" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C231">
         <v>345</v>
@@ -13339,7 +14395,7 @@
         <v>176</v>
       </c>
       <c r="B232" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="C232">
         <v>387</v>
@@ -13392,7 +14448,7 @@
         <v>222</v>
       </c>
       <c r="B233" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C233">
         <v>93</v>
@@ -13445,7 +14501,7 @@
         <v>328</v>
       </c>
       <c r="B234" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="C234">
         <v>80</v>
@@ -13496,6 +14552,9 @@
     <row r="235" spans="1:17">
       <c r="A235">
         <v>0</v>
+      </c>
+      <c r="B235" t="s">
+        <v>194</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -13548,7 +14607,7 @@
         <v>367</v>
       </c>
       <c r="B236" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="C236">
         <v>267</v>
@@ -13601,7 +14660,7 @@
         <v>355</v>
       </c>
       <c r="B237" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C237">
         <v>281</v>
@@ -13654,7 +14713,7 @@
         <v>317</v>
       </c>
       <c r="B238" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="C238">
         <v>313</v>
@@ -13707,7 +14766,7 @@
         <v>233</v>
       </c>
       <c r="B239" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="C239">
         <v>222</v>
@@ -13760,7 +14819,7 @@
         <v>404</v>
       </c>
       <c r="B240" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="C240">
         <v>327</v>
@@ -13813,7 +14872,7 @@
         <v>50</v>
       </c>
       <c r="B241" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="C241">
         <v>463</v>
@@ -13865,6 +14924,9 @@
       <c r="A242">
         <v>504</v>
       </c>
+      <c r="B242" t="s">
+        <v>199</v>
+      </c>
       <c r="C242">
         <v>217</v>
       </c>
@@ -13916,7 +14978,7 @@
         <v>396</v>
       </c>
       <c r="B243" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="C243">
         <v>219</v>
@@ -13969,7 +15031,7 @@
         <v>314</v>
       </c>
       <c r="B244" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="C244">
         <v>388</v>
@@ -14022,7 +15084,7 @@
         <v>315</v>
       </c>
       <c r="B245" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="C245">
         <v>180</v>
@@ -14075,7 +15137,7 @@
         <v>302</v>
       </c>
       <c r="B246" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C246">
         <v>108</v>
@@ -14128,7 +15190,7 @@
         <v>406</v>
       </c>
       <c r="B247" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="C247">
         <v>123</v>
@@ -14180,6 +15242,9 @@
       <c r="A248">
         <v>441</v>
       </c>
+      <c r="B248" t="s">
+        <v>202</v>
+      </c>
       <c r="C248">
         <v>298</v>
       </c>
@@ -14231,7 +15296,7 @@
         <v>381</v>
       </c>
       <c r="B249" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="C249">
         <v>314</v>
@@ -14284,7 +15349,7 @@
         <v>150</v>
       </c>
       <c r="B250" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="C250">
         <v>321</v>
@@ -14337,7 +15402,7 @@
         <v>281</v>
       </c>
       <c r="B251" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C251">
         <v>153</v>
@@ -14390,7 +15455,7 @@
         <v>203</v>
       </c>
       <c r="B252" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="C252">
         <v>234</v>
@@ -14443,7 +15508,7 @@
         <v>144</v>
       </c>
       <c r="B253" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="C253">
         <v>219</v>
@@ -14496,7 +15561,7 @@
         <v>202</v>
       </c>
       <c r="B254" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C254">
         <v>162</v>
@@ -14549,7 +15614,7 @@
         <v>347</v>
       </c>
       <c r="B255" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="C255">
         <v>118</v>
@@ -14602,7 +15667,7 @@
         <v>318</v>
       </c>
       <c r="B256" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C256">
         <v>233</v>
@@ -14655,7 +15720,7 @@
         <v>295</v>
       </c>
       <c r="B257" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="C257">
         <v>167</v>
@@ -14707,6 +15772,9 @@
       <c r="A258">
         <v>433</v>
       </c>
+      <c r="B258" t="s">
+        <v>208</v>
+      </c>
       <c r="C258">
         <v>169</v>
       </c>
@@ -14758,7 +15826,7 @@
         <v>376</v>
       </c>
       <c r="B259" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="C259">
         <v>139</v>
@@ -14811,7 +15879,7 @@
         <v>360</v>
       </c>
       <c r="B260" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C260">
         <v>227</v>
@@ -14864,7 +15932,7 @@
         <v>320</v>
       </c>
       <c r="B261" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="C261">
         <v>265</v>
@@ -14917,7 +15985,7 @@
         <v>224</v>
       </c>
       <c r="B262" t="s">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="C262">
         <v>90</v>
@@ -14970,7 +16038,7 @@
         <v>174</v>
       </c>
       <c r="B263" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="C263">
         <v>197</v>
@@ -15023,7 +16091,7 @@
         <v>286</v>
       </c>
       <c r="B264" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="C264">
         <v>243</v>
@@ -15076,7 +16144,7 @@
         <v>242</v>
       </c>
       <c r="B265" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="C265">
         <v>220</v>
@@ -15129,7 +16197,7 @@
         <v>282</v>
       </c>
       <c r="B266" t="s">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="C266">
         <v>143</v>
@@ -15182,7 +16250,7 @@
         <v>341</v>
       </c>
       <c r="B267" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C267">
         <v>178</v>
@@ -15235,7 +16303,7 @@
         <v>135</v>
       </c>
       <c r="B268" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="C268">
         <v>378</v>
@@ -15288,7 +16356,7 @@
         <v>308</v>
       </c>
       <c r="B269" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C269">
         <v>270</v>
@@ -15341,7 +16409,7 @@
         <v>305</v>
       </c>
       <c r="B270" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C270">
         <v>261</v>
@@ -15394,7 +16462,7 @@
         <v>251</v>
       </c>
       <c r="B271" t="s">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="C271">
         <v>300</v>
@@ -15447,7 +16515,7 @@
         <v>378</v>
       </c>
       <c r="B272" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="C272">
         <v>372</v>
@@ -15500,7 +16568,7 @@
         <v>301</v>
       </c>
       <c r="B273" t="s">
-        <v>184</v>
+        <v>217</v>
       </c>
       <c r="C273">
         <v>230</v>
@@ -15553,7 +16621,7 @@
         <v>214</v>
       </c>
       <c r="B274" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="C274">
         <v>183</v>
@@ -15606,7 +16674,7 @@
         <v>390</v>
       </c>
       <c r="B275" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C275">
         <v>131</v>
@@ -15659,7 +16727,7 @@
         <v>135</v>
       </c>
       <c r="B276" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="C276">
         <v>232</v>
@@ -15712,7 +16780,7 @@
         <v>142</v>
       </c>
       <c r="B277" t="s">
-        <v>185</v>
+        <v>218</v>
       </c>
       <c r="C277">
         <v>282</v>
@@ -15765,7 +16833,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="C278">
         <v>235</v>
@@ -15818,7 +16886,7 @@
         <v>302</v>
       </c>
       <c r="B279" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C279">
         <v>261</v>
@@ -15871,7 +16939,7 @@
         <v>211</v>
       </c>
       <c r="B280" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C280">
         <v>134</v>
@@ -15924,7 +16992,7 @@
         <v>125</v>
       </c>
       <c r="B281" t="s">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="C281">
         <v>140</v>
@@ -15976,6 +17044,9 @@
       <c r="A282">
         <v>449</v>
       </c>
+      <c r="B282" t="s">
+        <v>221</v>
+      </c>
       <c r="C282">
         <v>163</v>
       </c>
@@ -16027,7 +17098,7 @@
         <v>240</v>
       </c>
       <c r="B283" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C283">
         <v>128</v>
@@ -16080,7 +17151,7 @@
         <v>420</v>
       </c>
       <c r="B284" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C284">
         <v>238</v>
@@ -16133,7 +17204,7 @@
         <v>305</v>
       </c>
       <c r="B285" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C285">
         <v>443</v>
@@ -16186,7 +17257,7 @@
         <v>395</v>
       </c>
       <c r="B286" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="C286">
         <v>270</v>
@@ -16239,7 +17310,7 @@
         <v>337</v>
       </c>
       <c r="B287" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C287">
         <v>161</v>
@@ -16292,7 +17363,7 @@
         <v>324</v>
       </c>
       <c r="B288" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C288">
         <v>139</v>
@@ -16345,7 +17416,7 @@
         <v>180</v>
       </c>
       <c r="B289" t="s">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="C289">
         <v>275</v>
@@ -16398,7 +17469,7 @@
         <v>241</v>
       </c>
       <c r="B290" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C290">
         <v>160</v>
@@ -16451,7 +17522,7 @@
         <v>180</v>
       </c>
       <c r="B291" t="s">
-        <v>189</v>
+        <v>223</v>
       </c>
       <c r="C291">
         <v>128</v>
@@ -16504,7 +17575,7 @@
         <v>281</v>
       </c>
       <c r="B292" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C292">
         <v>266</v>
@@ -16557,7 +17628,7 @@
         <v>375</v>
       </c>
       <c r="B293" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C293">
         <v>123</v>
@@ -16610,7 +17681,7 @@
         <v>335</v>
       </c>
       <c r="B294" t="s">
-        <v>190</v>
+        <v>224</v>
       </c>
       <c r="C294">
         <v>195</v>
@@ -16663,7 +17734,7 @@
         <v>300</v>
       </c>
       <c r="B295" t="s">
-        <v>191</v>
+        <v>225</v>
       </c>
       <c r="C295">
         <v>205</v>
@@ -16716,7 +17787,7 @@
         <v>268</v>
       </c>
       <c r="B296" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="C296">
         <v>143</v>
@@ -16769,7 +17840,7 @@
         <v>347</v>
       </c>
       <c r="B297" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="C297">
         <v>134</v>
@@ -16822,7 +17893,7 @@
         <v>267</v>
       </c>
       <c r="B298" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C298">
         <v>222</v>
@@ -16875,7 +17946,7 @@
         <v>101</v>
       </c>
       <c r="B299" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="C299">
         <v>198</v>
@@ -16928,7 +17999,7 @@
         <v>359</v>
       </c>
       <c r="B300" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C300">
         <v>58</v>
@@ -16981,7 +18052,7 @@
         <v>371</v>
       </c>
       <c r="B301" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="C301">
         <v>269</v>
@@ -17034,7 +18105,7 @@
         <v>190</v>
       </c>
       <c r="B302" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="C302">
         <v>101</v>
@@ -17086,6 +18157,9 @@
       <c r="A303">
         <v>524</v>
       </c>
+      <c r="B303" t="s">
+        <v>230</v>
+      </c>
       <c r="C303">
         <v>125</v>
       </c>
@@ -17137,7 +18211,7 @@
         <v>270</v>
       </c>
       <c r="B304" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="C304">
         <v>151</v>
@@ -17190,7 +18264,7 @@
         <v>242</v>
       </c>
       <c r="B305" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="C305">
         <v>180</v>
@@ -17243,7 +18317,7 @@
         <v>354</v>
       </c>
       <c r="B306" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="C306">
         <v>162</v>
@@ -17296,7 +18370,7 @@
         <v>399</v>
       </c>
       <c r="B307" t="s">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="C307">
         <v>136</v>
@@ -17349,7 +18423,7 @@
         <v>411</v>
       </c>
       <c r="B308" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C308">
         <v>260</v>
@@ -17402,7 +18476,7 @@
         <v>190</v>
       </c>
       <c r="B309" t="s">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="C309">
         <v>183</v>
@@ -17455,7 +18529,7 @@
         <v>305</v>
       </c>
       <c r="B310" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C310">
         <v>350</v>
@@ -17508,7 +18582,7 @@
         <v>226</v>
       </c>
       <c r="B311" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="C311">
         <v>167</v>
@@ -17561,7 +18635,7 @@
         <v>93</v>
       </c>
       <c r="B312" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="C312">
         <v>255</v>
@@ -17614,7 +18688,7 @@
         <v>178</v>
       </c>
       <c r="B313" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C313">
         <v>212</v>
@@ -17667,7 +18741,7 @@
         <v>372</v>
       </c>
       <c r="B314" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="C314">
         <v>327</v>
@@ -17720,7 +18794,7 @@
         <v>250</v>
       </c>
       <c r="B315" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C315">
         <v>294</v>
@@ -17773,7 +18847,7 @@
         <v>308</v>
       </c>
       <c r="B316" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C316">
         <v>214</v>
@@ -17826,7 +18900,7 @@
         <v>201</v>
       </c>
       <c r="B317" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="C317">
         <v>249</v>
@@ -17879,7 +18953,7 @@
         <v>126</v>
       </c>
       <c r="B318" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="C318">
         <v>250</v>
@@ -17931,6 +19005,9 @@
       <c r="A319">
         <v>464</v>
       </c>
+      <c r="B319" t="s">
+        <v>236</v>
+      </c>
       <c r="C319">
         <v>187</v>
       </c>
@@ -17982,7 +19059,7 @@
         <v>306</v>
       </c>
       <c r="B320" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="C320">
         <v>196</v>
@@ -18035,7 +19112,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="C321">
         <v>281</v>
@@ -18088,7 +19165,7 @@
         <v>364</v>
       </c>
       <c r="B322" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="C322">
         <v>243</v>
@@ -18140,6 +19217,9 @@
       <c r="A323">
         <v>512</v>
       </c>
+      <c r="B323" t="s">
+        <v>238</v>
+      </c>
       <c r="C323">
         <v>159</v>
       </c>
@@ -18191,7 +19271,7 @@
         <v>268</v>
       </c>
       <c r="B324" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="C324">
         <v>69</v>
@@ -18244,7 +19324,7 @@
         <v>174</v>
       </c>
       <c r="B325" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="C325">
         <v>342</v>
@@ -18297,7 +19377,7 @@
         <v>416</v>
       </c>
       <c r="B326" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="C326">
         <v>261</v>
@@ -18350,7 +19430,7 @@
         <v>377</v>
       </c>
       <c r="B327" t="s">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="C327">
         <v>198</v>
@@ -18403,7 +19483,7 @@
         <v>334</v>
       </c>
       <c r="B328" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C328">
         <v>243</v>
@@ -18456,7 +19536,7 @@
         <v>10</v>
       </c>
       <c r="B329" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="C329">
         <v>353</v>
@@ -18509,7 +19589,7 @@
         <v>54</v>
       </c>
       <c r="B330" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="C330">
         <v>289</v>
@@ -18562,7 +19642,7 @@
         <v>34</v>
       </c>
       <c r="B331" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="C331">
         <v>247</v>
@@ -18615,7 +19695,7 @@
         <v>294</v>
       </c>
       <c r="B332" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C332">
         <v>121</v>
@@ -18668,7 +19748,7 @@
         <v>68</v>
       </c>
       <c r="B333" t="s">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="C333">
         <v>279</v>
@@ -18721,7 +19801,7 @@
         <v>60</v>
       </c>
       <c r="B334" t="s">
-        <v>207</v>
+        <v>244</v>
       </c>
       <c r="C334">
         <v>457</v>
@@ -18774,7 +19854,7 @@
         <v>413</v>
       </c>
       <c r="B335" t="s">
-        <v>208</v>
+        <v>245</v>
       </c>
       <c r="C335">
         <v>206</v>
@@ -18826,6 +19906,9 @@
       <c r="A336">
         <v>456</v>
       </c>
+      <c r="B336" t="s">
+        <v>246</v>
+      </c>
       <c r="C336">
         <v>159</v>
       </c>
@@ -18877,7 +19960,7 @@
         <v>220</v>
       </c>
       <c r="B337" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="C337">
         <v>309</v>
@@ -18930,7 +20013,7 @@
         <v>248</v>
       </c>
       <c r="B338" t="s">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="C338">
         <v>247</v>
@@ -18983,7 +20066,7 @@
         <v>311</v>
       </c>
       <c r="B339" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C339">
         <v>233</v>
@@ -19036,7 +20119,7 @@
         <v>221</v>
       </c>
       <c r="B340" t="s">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="C340">
         <v>237</v>
@@ -19089,7 +20172,7 @@
         <v>367</v>
       </c>
       <c r="B341" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="C341">
         <v>162</v>
@@ -19142,7 +20225,7 @@
         <v>169</v>
       </c>
       <c r="B342" t="s">
-        <v>211</v>
+        <v>249</v>
       </c>
       <c r="C342">
         <v>208</v>
@@ -19195,7 +20278,7 @@
         <v>383</v>
       </c>
       <c r="B343" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C343">
         <v>205</v>
@@ -19248,7 +20331,7 @@
         <v>259</v>
       </c>
       <c r="B344" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="C344">
         <v>106</v>
@@ -19301,7 +20384,7 @@
         <v>230</v>
       </c>
       <c r="B345" t="s">
-        <v>213</v>
+        <v>251</v>
       </c>
       <c r="C345">
         <v>324</v>
@@ -19354,7 +20437,7 @@
         <v>223</v>
       </c>
       <c r="B346" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="C346">
         <v>58</v>
@@ -19407,7 +20490,7 @@
         <v>365</v>
       </c>
       <c r="B347" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="C347">
         <v>257</v>
@@ -19460,7 +20543,7 @@
         <v>101</v>
       </c>
       <c r="B348" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="C348">
         <v>87</v>
@@ -19513,7 +20596,7 @@
         <v>257</v>
       </c>
       <c r="B349" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C349">
         <v>459</v>
@@ -19566,7 +20649,7 @@
         <v>282</v>
       </c>
       <c r="B350" t="s">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="C350">
         <v>328</v>
@@ -19619,7 +20702,7 @@
         <v>244</v>
       </c>
       <c r="B351" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C351">
         <v>177</v>
@@ -19672,7 +20755,7 @@
         <v>35</v>
       </c>
       <c r="B352" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="C352">
         <v>303</v>
@@ -19725,7 +20808,7 @@
         <v>266</v>
       </c>
       <c r="B353" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="C353">
         <v>197</v>
@@ -19778,7 +20861,7 @@
         <v>198</v>
       </c>
       <c r="B354" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="C354">
         <v>194</v>
@@ -19830,6 +20913,9 @@
       <c r="A355">
         <v>467</v>
       </c>
+      <c r="B355" t="s">
+        <v>257</v>
+      </c>
       <c r="C355">
         <v>297</v>
       </c>
@@ -19881,7 +20967,7 @@
         <v>274</v>
       </c>
       <c r="B356" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="C356">
         <v>308</v>
@@ -19934,7 +21020,7 @@
         <v>249</v>
       </c>
       <c r="B357" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C357">
         <v>201</v>
@@ -19987,7 +21073,7 @@
         <v>280</v>
       </c>
       <c r="B358" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="C358">
         <v>110</v>
@@ -20040,7 +21126,7 @@
         <v>78</v>
       </c>
       <c r="B359" t="s">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="C359">
         <v>375</v>
@@ -20093,7 +21179,7 @@
         <v>256</v>
       </c>
       <c r="B360" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C360">
         <v>239</v>
@@ -20146,7 +21232,7 @@
         <v>270</v>
       </c>
       <c r="B361" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="C361">
         <v>339</v>
@@ -20199,7 +21285,7 @@
         <v>410</v>
       </c>
       <c r="B362" t="s">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="C362">
         <v>278</v>
@@ -20252,7 +21338,7 @@
         <v>342</v>
       </c>
       <c r="B363" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C363">
         <v>171</v>
@@ -20305,7 +21391,7 @@
         <v>416</v>
       </c>
       <c r="B364" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="C364">
         <v>130</v>
@@ -20358,7 +21444,7 @@
         <v>308</v>
       </c>
       <c r="B365" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C365">
         <v>182</v>
@@ -20411,7 +21497,7 @@
         <v>44</v>
       </c>
       <c r="B366" t="s">
-        <v>222</v>
+        <v>261</v>
       </c>
       <c r="C366">
         <v>287</v>
@@ -20464,7 +21550,7 @@
         <v>35</v>
       </c>
       <c r="B367" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="C367">
         <v>301</v>
@@ -20517,7 +21603,7 @@
         <v>306</v>
       </c>
       <c r="B368" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="C368">
         <v>117</v>
@@ -20570,7 +21656,7 @@
         <v>143</v>
       </c>
       <c r="B369" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="C369">
         <v>162</v>
@@ -20623,7 +21709,7 @@
         <v>182</v>
       </c>
       <c r="B370" t="s">
-        <v>223</v>
+        <v>262</v>
       </c>
       <c r="C370">
         <v>449</v>
@@ -20676,7 +21762,7 @@
         <v>274</v>
       </c>
       <c r="B371" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="C371">
         <v>167</v>
@@ -20729,7 +21815,7 @@
         <v>266</v>
       </c>
       <c r="B372" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="C372">
         <v>280</v>
@@ -20782,7 +21868,7 @@
         <v>108</v>
       </c>
       <c r="B373" t="s">
-        <v>224</v>
+        <v>263</v>
       </c>
       <c r="C373">
         <v>54</v>
@@ -20835,7 +21921,7 @@
         <v>287</v>
       </c>
       <c r="B374" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C374">
         <v>208</v>
@@ -20888,7 +21974,7 @@
         <v>326</v>
       </c>
       <c r="B375" t="s">
-        <v>225</v>
+        <v>264</v>
       </c>
       <c r="C375">
         <v>109</v>
@@ -20941,7 +22027,7 @@
         <v>172</v>
       </c>
       <c r="B376" t="s">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="C376">
         <v>156</v>
@@ -20994,7 +22080,7 @@
         <v>292</v>
       </c>
       <c r="B377" t="s">
-        <v>227</v>
+        <v>266</v>
       </c>
       <c r="C377">
         <v>355</v>
@@ -21047,7 +22133,7 @@
         <v>202</v>
       </c>
       <c r="B378" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C378">
         <v>181</v>
@@ -21100,7 +22186,7 @@
         <v>243</v>
       </c>
       <c r="B379" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C379">
         <v>164</v>
@@ -21153,7 +22239,7 @@
         <v>277</v>
       </c>
       <c r="B380" t="s">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="C380">
         <v>174</v>
@@ -21206,7 +22292,7 @@
         <v>102</v>
       </c>
       <c r="B381" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C381">
         <v>278</v>
@@ -21259,7 +22345,7 @@
         <v>322</v>
       </c>
       <c r="B382" t="s">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="C382">
         <v>323</v>
@@ -21312,7 +22398,7 @@
         <v>271</v>
       </c>
       <c r="B383" t="s">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="C383">
         <v>188</v>
@@ -21365,7 +22451,7 @@
         <v>227</v>
       </c>
       <c r="B384" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C384">
         <v>112</v>
@@ -21418,7 +22504,7 @@
         <v>236</v>
       </c>
       <c r="B385" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C385">
         <v>189</v>
@@ -21471,7 +22557,7 @@
         <v>267</v>
       </c>
       <c r="B386" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C386">
         <v>176</v>
@@ -21524,7 +22610,7 @@
         <v>253</v>
       </c>
       <c r="B387" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C387">
         <v>203</v>
@@ -21577,7 +22663,7 @@
         <v>257</v>
       </c>
       <c r="B388" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C388">
         <v>180</v>
@@ -21629,6 +22715,9 @@
       <c r="A389">
         <v>522</v>
       </c>
+      <c r="B389" t="s">
+        <v>270</v>
+      </c>
       <c r="C389">
         <v>241</v>
       </c>
@@ -21680,7 +22769,7 @@
         <v>382</v>
       </c>
       <c r="B390" t="s">
-        <v>231</v>
+        <v>271</v>
       </c>
       <c r="C390">
         <v>325</v>
@@ -21733,7 +22822,7 @@
         <v>380</v>
       </c>
       <c r="B391" t="s">
-        <v>232</v>
+        <v>272</v>
       </c>
       <c r="C391">
         <v>151</v>
@@ -21786,7 +22875,7 @@
         <v>38</v>
       </c>
       <c r="B392" t="s">
-        <v>233</v>
+        <v>273</v>
       </c>
       <c r="C392">
         <v>379</v>
@@ -21839,7 +22928,7 @@
         <v>171</v>
       </c>
       <c r="B393" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="C393">
         <v>356</v>
@@ -21892,7 +22981,7 @@
         <v>259</v>
       </c>
       <c r="B394" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="C394">
         <v>350</v>
@@ -21945,7 +23034,7 @@
         <v>51</v>
       </c>
       <c r="B395" t="s">
-        <v>234</v>
+        <v>274</v>
       </c>
       <c r="C395">
         <v>253</v>
@@ -21998,7 +23087,7 @@
         <v>183</v>
       </c>
       <c r="B396" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C396">
         <v>155</v>
@@ -22051,7 +23140,7 @@
         <v>412</v>
       </c>
       <c r="B397" t="s">
-        <v>235</v>
+        <v>275</v>
       </c>
       <c r="C397">
         <v>217</v>
@@ -22104,7 +23193,7 @@
         <v>154</v>
       </c>
       <c r="B398" t="s">
-        <v>236</v>
+        <v>276</v>
       </c>
       <c r="C398">
         <v>186</v>
@@ -22157,7 +23246,7 @@
         <v>229</v>
       </c>
       <c r="B399" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="C399">
         <v>170</v>
@@ -22210,7 +23299,7 @@
         <v>191</v>
       </c>
       <c r="B400" t="s">
-        <v>237</v>
+        <v>277</v>
       </c>
       <c r="C400">
         <v>137</v>
@@ -22263,7 +23352,7 @@
         <v>328</v>
       </c>
       <c r="B401" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="C401">
         <v>215</v>
@@ -22316,7 +23405,7 @@
         <v>308</v>
       </c>
       <c r="B402" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C402">
         <v>291</v>
@@ -22369,7 +23458,7 @@
         <v>213</v>
       </c>
       <c r="B403" t="s">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="C403">
         <v>249</v>
@@ -22422,7 +23511,7 @@
         <v>237</v>
       </c>
       <c r="B404" t="s">
-        <v>239</v>
+        <v>279</v>
       </c>
       <c r="C404">
         <v>111</v>
@@ -22475,7 +23564,7 @@
         <v>276</v>
       </c>
       <c r="B405" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="C405">
         <v>166</v>
@@ -22528,7 +23617,7 @@
         <v>361</v>
       </c>
       <c r="B406" t="s">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="C406">
         <v>243</v>
@@ -22581,7 +23670,7 @@
         <v>327</v>
       </c>
       <c r="B407" t="s">
-        <v>241</v>
+        <v>281</v>
       </c>
       <c r="C407">
         <v>226</v>
@@ -22634,7 +23723,7 @@
         <v>216</v>
       </c>
       <c r="B408" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C408">
         <v>85</v>
@@ -22687,7 +23776,7 @@
         <v>421</v>
       </c>
       <c r="B409" t="s">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="C409">
         <v>196</v>
@@ -22740,7 +23829,7 @@
         <v>279</v>
       </c>
       <c r="B410" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C410">
         <v>251</v>
@@ -22793,7 +23882,7 @@
         <v>126</v>
       </c>
       <c r="B411" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="C411">
         <v>47</v>
@@ -22846,7 +23935,7 @@
         <v>275</v>
       </c>
       <c r="B412" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C412">
         <v>191</v>
@@ -22899,7 +23988,7 @@
         <v>276</v>
       </c>
       <c r="B413" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="C413">
         <v>182</v>
@@ -22952,7 +24041,7 @@
         <v>167</v>
       </c>
       <c r="B414" t="s">
-        <v>243</v>
+        <v>283</v>
       </c>
       <c r="C414">
         <v>153</v>
@@ -23005,7 +24094,7 @@
         <v>359</v>
       </c>
       <c r="B415" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C415">
         <v>203</v>
@@ -23058,7 +24147,7 @@
         <v>176</v>
       </c>
       <c r="B416" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="C416">
         <v>331</v>
@@ -23111,7 +24200,7 @@
         <v>217</v>
       </c>
       <c r="B417" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="C417">
         <v>235</v>
@@ -23164,7 +24253,7 @@
         <v>193</v>
       </c>
       <c r="B418" t="s">
-        <v>244</v>
+        <v>284</v>
       </c>
       <c r="C418">
         <v>293</v>
@@ -23217,7 +24306,7 @@
         <v>179</v>
       </c>
       <c r="B419" t="s">
-        <v>245</v>
+        <v>285</v>
       </c>
       <c r="C419">
         <v>431</v>
@@ -23270,7 +24359,7 @@
         <v>259</v>
       </c>
       <c r="B420" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="C420">
         <v>302</v>
@@ -23323,7 +24412,7 @@
         <v>277</v>
       </c>
       <c r="B421" t="s">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="C421">
         <v>355</v>
@@ -23376,7 +24465,7 @@
         <v>232</v>
       </c>
       <c r="B422" t="s">
-        <v>246</v>
+        <v>286</v>
       </c>
       <c r="C422">
         <v>278</v>
@@ -23429,7 +24518,7 @@
         <v>404</v>
       </c>
       <c r="B423" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="C423">
         <v>220</v>
@@ -23481,6 +24570,9 @@
       <c r="A424">
         <v>454</v>
       </c>
+      <c r="B424" t="s">
+        <v>287</v>
+      </c>
       <c r="C424">
         <v>168</v>
       </c>
@@ -23532,7 +24624,7 @@
         <v>403</v>
       </c>
       <c r="B425" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="C425">
         <v>233</v>
@@ -23585,7 +24677,7 @@
         <v>338</v>
       </c>
       <c r="B426" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="C426">
         <v>154</v>
@@ -23638,7 +24730,7 @@
         <v>224</v>
       </c>
       <c r="B427" t="s">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="C427">
         <v>426</v>
@@ -23691,7 +24783,7 @@
         <v>365</v>
       </c>
       <c r="B428" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="C428">
         <v>249</v>
@@ -23744,7 +24836,7 @@
         <v>208</v>
       </c>
       <c r="B429" t="s">
-        <v>247</v>
+        <v>288</v>
       </c>
       <c r="C429">
         <v>478</v>
@@ -23797,7 +24889,7 @@
         <v>391</v>
       </c>
       <c r="B430" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="C430">
         <v>277</v>
@@ -23850,7 +24942,7 @@
         <v>278</v>
       </c>
       <c r="B431" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C431">
         <v>378</v>
@@ -23903,7 +24995,7 @@
         <v>366</v>
       </c>
       <c r="B432" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="C432">
         <v>220</v>
@@ -23955,6 +25047,9 @@
       <c r="A433">
         <v>441</v>
       </c>
+      <c r="B433" t="s">
+        <v>291</v>
+      </c>
       <c r="C433">
         <v>234</v>
       </c>
@@ -24006,7 +25101,7 @@
         <v>403</v>
       </c>
       <c r="B434" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="C434">
         <v>246</v>
@@ -24059,7 +25154,7 @@
         <v>346</v>
       </c>
       <c r="B435" t="s">
-        <v>250</v>
+        <v>292</v>
       </c>
       <c r="C435">
         <v>350</v>
@@ -24112,7 +25207,7 @@
         <v>416</v>
       </c>
       <c r="B436" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="C436">
         <v>162</v>
@@ -24165,7 +25260,7 @@
         <v>302</v>
       </c>
       <c r="B437" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C437">
         <v>236</v>
@@ -24218,7 +25313,7 @@
         <v>191</v>
       </c>
       <c r="B438" t="s">
-        <v>237</v>
+        <v>277</v>
       </c>
       <c r="C438">
         <v>33</v>
@@ -24271,7 +25366,7 @@
         <v>131</v>
       </c>
       <c r="B439" t="s">
-        <v>251</v>
+        <v>293</v>
       </c>
       <c r="C439">
         <v>531</v>
@@ -24324,7 +25419,7 @@
         <v>252</v>
       </c>
       <c r="B440" t="s">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="C440">
         <v>96</v>
@@ -24377,7 +25472,7 @@
         <v>311</v>
       </c>
       <c r="B441" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C441">
         <v>237</v>
@@ -24430,7 +25525,7 @@
         <v>160</v>
       </c>
       <c r="B442" t="s">
-        <v>253</v>
+        <v>295</v>
       </c>
       <c r="C442">
         <v>339</v>
@@ -24483,7 +25578,7 @@
         <v>255</v>
       </c>
       <c r="B443" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C443">
         <v>73</v>
@@ -24536,7 +25631,7 @@
         <v>290</v>
       </c>
       <c r="B444" t="s">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="C444">
         <v>209</v>
@@ -24589,7 +25684,7 @@
         <v>317</v>
       </c>
       <c r="B445" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="C445">
         <v>233</v>
@@ -24641,6 +25736,9 @@
       <c r="A446">
         <v>454</v>
       </c>
+      <c r="B446" t="s">
+        <v>297</v>
+      </c>
       <c r="C446">
         <v>143</v>
       </c>
@@ -24692,7 +25790,7 @@
         <v>188</v>
       </c>
       <c r="B447" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C447">
         <v>531</v>
@@ -24745,7 +25843,7 @@
         <v>414</v>
       </c>
       <c r="B448" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="C448">
         <v>287</v>
@@ -24798,7 +25896,7 @@
         <v>409</v>
       </c>
       <c r="B449" t="s">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="C449">
         <v>310</v>
@@ -24851,7 +25949,7 @@
         <v>163</v>
       </c>
       <c r="B450" t="s">
-        <v>257</v>
+        <v>300</v>
       </c>
       <c r="C450">
         <v>267</v>
@@ -24904,7 +26002,7 @@
         <v>288</v>
       </c>
       <c r="B451" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C451">
         <v>282</v>
@@ -24956,6 +26054,9 @@
       <c r="A452">
         <v>446</v>
       </c>
+      <c r="B452" t="s">
+        <v>301</v>
+      </c>
       <c r="C452">
         <v>214</v>
       </c>
@@ -25007,7 +26108,7 @@
         <v>325</v>
       </c>
       <c r="B453" t="s">
-        <v>258</v>
+        <v>302</v>
       </c>
       <c r="C453">
         <v>267</v>
@@ -25060,7 +26161,7 @@
         <v>213</v>
       </c>
       <c r="B454" t="s">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="C454">
         <v>184</v>
@@ -25113,7 +26214,7 @@
         <v>232</v>
       </c>
       <c r="B455" t="s">
-        <v>246</v>
+        <v>286</v>
       </c>
       <c r="C455">
         <v>281</v>
@@ -25166,7 +26267,7 @@
         <v>128</v>
       </c>
       <c r="B456" t="s">
-        <v>259</v>
+        <v>303</v>
       </c>
       <c r="C456">
         <v>71</v>
@@ -25219,7 +26320,7 @@
         <v>285</v>
       </c>
       <c r="B457" t="s">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="C457">
         <v>201</v>
@@ -25272,7 +26373,7 @@
         <v>94</v>
       </c>
       <c r="B458" t="s">
-        <v>261</v>
+        <v>305</v>
       </c>
       <c r="C458">
         <v>57</v>
@@ -25325,7 +26426,7 @@
         <v>214</v>
       </c>
       <c r="B459" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="C459">
         <v>132</v>
@@ -25378,7 +26479,7 @@
         <v>246</v>
       </c>
       <c r="B460" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C460">
         <v>87</v>
@@ -25431,7 +26532,7 @@
         <v>393</v>
       </c>
       <c r="B461" t="s">
-        <v>262</v>
+        <v>306</v>
       </c>
       <c r="C461">
         <v>126</v>
@@ -25484,7 +26585,7 @@
         <v>355</v>
       </c>
       <c r="B462" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C462">
         <v>184</v>
@@ -25537,7 +26638,7 @@
         <v>285</v>
       </c>
       <c r="B463" t="s">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="C463">
         <v>241</v>
@@ -25590,7 +26691,7 @@
         <v>367</v>
       </c>
       <c r="B464" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="C464">
         <v>261</v>
@@ -25642,6 +26743,9 @@
       <c r="A465">
         <v>455</v>
       </c>
+      <c r="B465" t="s">
+        <v>307</v>
+      </c>
       <c r="C465">
         <v>71</v>
       </c>
@@ -25693,7 +26797,7 @@
         <v>318</v>
       </c>
       <c r="B466" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C466">
         <v>181</v>
@@ -25746,7 +26850,7 @@
         <v>282</v>
       </c>
       <c r="B467" t="s">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="C467">
         <v>126</v>
@@ -25799,7 +26903,7 @@
         <v>245</v>
       </c>
       <c r="B468" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="C468">
         <v>177</v>
@@ -25852,7 +26956,7 @@
         <v>274</v>
       </c>
       <c r="B469" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="C469">
         <v>188</v>
@@ -25905,7 +27009,7 @@
         <v>149</v>
       </c>
       <c r="B470" t="s">
-        <v>263</v>
+        <v>308</v>
       </c>
       <c r="C470">
         <v>295</v>
@@ -25958,7 +27062,7 @@
         <v>231</v>
       </c>
       <c r="B471" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C471">
         <v>325</v>
@@ -26011,7 +27115,7 @@
         <v>154</v>
       </c>
       <c r="B472" t="s">
-        <v>236</v>
+        <v>276</v>
       </c>
       <c r="C472">
         <v>195</v>
@@ -26064,7 +27168,7 @@
         <v>291</v>
       </c>
       <c r="B473" t="s">
-        <v>264</v>
+        <v>309</v>
       </c>
       <c r="C473">
         <v>340</v>
@@ -26117,7 +27221,7 @@
         <v>271</v>
       </c>
       <c r="B474" t="s">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="C474">
         <v>170</v>
@@ -26170,7 +27274,7 @@
         <v>110</v>
       </c>
       <c r="B475" t="s">
-        <v>265</v>
+        <v>310</v>
       </c>
       <c r="C475">
         <v>95</v>
@@ -26222,6 +27326,9 @@
       <c r="A476">
         <v>0</v>
       </c>
+      <c r="B476" t="s">
+        <v>311</v>
+      </c>
       <c r="C476">
         <v>0</v>
       </c>
@@ -26271,6 +27378,9 @@
     <row r="477" spans="1:17">
       <c r="A477">
         <v>0</v>
+      </c>
+      <c r="B477" t="s">
+        <v>312</v>
       </c>
       <c r="C477">
         <v>0</v>
@@ -26323,7 +27433,7 @@
         <v>339</v>
       </c>
       <c r="B478" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C478">
         <v>252</v>
@@ -26376,7 +27486,7 @@
         <v>386</v>
       </c>
       <c r="B479" t="s">
-        <v>266</v>
+        <v>313</v>
       </c>
       <c r="C479">
         <v>200</v>
@@ -26428,6 +27538,9 @@
       <c r="A480">
         <v>0</v>
       </c>
+      <c r="B480" t="s">
+        <v>314</v>
+      </c>
       <c r="C480">
         <v>0</v>
       </c>
@@ -26478,6 +27591,9 @@
       <c r="A481">
         <v>0</v>
       </c>
+      <c r="B481" t="s">
+        <v>315</v>
+      </c>
       <c r="C481">
         <v>0</v>
       </c>
@@ -26528,6 +27644,9 @@
       <c r="A482">
         <v>0</v>
       </c>
+      <c r="B482" t="s">
+        <v>316</v>
+      </c>
       <c r="C482">
         <v>0</v>
       </c>
@@ -26578,6 +27697,9 @@
       <c r="A483">
         <v>0</v>
       </c>
+      <c r="B483" t="s">
+        <v>317</v>
+      </c>
       <c r="C483">
         <v>0</v>
       </c>
@@ -26628,6 +27750,9 @@
       <c r="A484">
         <v>0</v>
       </c>
+      <c r="B484" t="s">
+        <v>318</v>
+      </c>
       <c r="C484">
         <v>0</v>
       </c>
@@ -26678,6 +27803,9 @@
       <c r="A485">
         <v>0</v>
       </c>
+      <c r="B485" t="s">
+        <v>319</v>
+      </c>
       <c r="C485">
         <v>0</v>
       </c>
@@ -26728,6 +27856,9 @@
       <c r="A486">
         <v>0</v>
       </c>
+      <c r="B486" t="s">
+        <v>320</v>
+      </c>
       <c r="C486">
         <v>0</v>
       </c>
@@ -26778,6 +27909,9 @@
       <c r="A487">
         <v>0</v>
       </c>
+      <c r="B487" t="s">
+        <v>321</v>
+      </c>
       <c r="C487">
         <v>0</v>
       </c>
@@ -26828,6 +27962,9 @@
       <c r="A488">
         <v>0</v>
       </c>
+      <c r="B488" t="s">
+        <v>322</v>
+      </c>
       <c r="C488">
         <v>0</v>
       </c>
@@ -26878,6 +28015,9 @@
       <c r="A489">
         <v>0</v>
       </c>
+      <c r="B489" t="s">
+        <v>323</v>
+      </c>
       <c r="C489">
         <v>0</v>
       </c>
@@ -26928,6 +28068,9 @@
       <c r="A490">
         <v>0</v>
       </c>
+      <c r="B490" t="s">
+        <v>324</v>
+      </c>
       <c r="C490">
         <v>0</v>
       </c>
@@ -26978,6 +28121,9 @@
       <c r="A491">
         <v>0</v>
       </c>
+      <c r="B491" t="s">
+        <v>325</v>
+      </c>
       <c r="C491">
         <v>0</v>
       </c>
@@ -27028,6 +28174,9 @@
       <c r="A492">
         <v>0</v>
       </c>
+      <c r="B492" t="s">
+        <v>326</v>
+      </c>
       <c r="C492">
         <v>0</v>
       </c>
@@ -27078,6 +28227,9 @@
       <c r="A493">
         <v>0</v>
       </c>
+      <c r="B493" t="s">
+        <v>327</v>
+      </c>
       <c r="C493">
         <v>0</v>
       </c>
@@ -27128,6 +28280,9 @@
       <c r="A494">
         <v>0</v>
       </c>
+      <c r="B494" t="s">
+        <v>328</v>
+      </c>
       <c r="C494">
         <v>0</v>
       </c>
@@ -27178,6 +28333,9 @@
       <c r="A495">
         <v>0</v>
       </c>
+      <c r="B495" t="s">
+        <v>329</v>
+      </c>
       <c r="C495">
         <v>0</v>
       </c>
@@ -27228,6 +28386,9 @@
       <c r="A496">
         <v>0</v>
       </c>
+      <c r="B496" t="s">
+        <v>330</v>
+      </c>
       <c r="C496">
         <v>0</v>
       </c>
@@ -27278,6 +28439,9 @@
       <c r="A497">
         <v>0</v>
       </c>
+      <c r="B497" t="s">
+        <v>331</v>
+      </c>
       <c r="C497">
         <v>0</v>
       </c>
@@ -27328,6 +28492,9 @@
       <c r="A498">
         <v>0</v>
       </c>
+      <c r="B498" t="s">
+        <v>332</v>
+      </c>
       <c r="C498">
         <v>0</v>
       </c>
@@ -27378,6 +28545,9 @@
       <c r="A499">
         <v>0</v>
       </c>
+      <c r="B499" t="s">
+        <v>333</v>
+      </c>
       <c r="C499">
         <v>0</v>
       </c>
@@ -27428,6 +28598,9 @@
       <c r="A500">
         <v>0</v>
       </c>
+      <c r="B500" t="s">
+        <v>334</v>
+      </c>
       <c r="C500">
         <v>0</v>
       </c>
@@ -27478,6 +28651,9 @@
       <c r="A501">
         <v>0</v>
       </c>
+      <c r="B501" t="s">
+        <v>335</v>
+      </c>
       <c r="C501">
         <v>0</v>
       </c>
@@ -27528,6 +28704,9 @@
       <c r="A502">
         <v>0</v>
       </c>
+      <c r="B502" t="s">
+        <v>336</v>
+      </c>
       <c r="C502">
         <v>0</v>
       </c>
@@ -27578,6 +28757,9 @@
       <c r="A503">
         <v>0</v>
       </c>
+      <c r="B503" t="s">
+        <v>337</v>
+      </c>
       <c r="C503">
         <v>0</v>
       </c>
@@ -27628,6 +28810,9 @@
       <c r="A504">
         <v>0</v>
       </c>
+      <c r="B504" t="s">
+        <v>338</v>
+      </c>
       <c r="C504">
         <v>0</v>
       </c>
@@ -27678,6 +28863,9 @@
       <c r="A505">
         <v>0</v>
       </c>
+      <c r="B505" t="s">
+        <v>339</v>
+      </c>
       <c r="C505">
         <v>0</v>
       </c>
@@ -27728,6 +28916,9 @@
       <c r="A506">
         <v>0</v>
       </c>
+      <c r="B506" t="s">
+        <v>340</v>
+      </c>
       <c r="C506">
         <v>0</v>
       </c>
@@ -27778,6 +28969,9 @@
       <c r="A507">
         <v>0</v>
       </c>
+      <c r="B507" t="s">
+        <v>341</v>
+      </c>
       <c r="C507">
         <v>0</v>
       </c>
@@ -27828,6 +29022,9 @@
       <c r="A508">
         <v>0</v>
       </c>
+      <c r="B508" t="s">
+        <v>342</v>
+      </c>
       <c r="C508">
         <v>0</v>
       </c>
@@ -27878,6 +29075,9 @@
       <c r="A509">
         <v>0</v>
       </c>
+      <c r="B509" t="s">
+        <v>343</v>
+      </c>
       <c r="C509">
         <v>0</v>
       </c>
@@ -27928,6 +29128,9 @@
       <c r="A510">
         <v>0</v>
       </c>
+      <c r="B510" t="s">
+        <v>344</v>
+      </c>
       <c r="C510">
         <v>0</v>
       </c>
@@ -27978,6 +29181,9 @@
       <c r="A511">
         <v>0</v>
       </c>
+      <c r="B511" t="s">
+        <v>345</v>
+      </c>
       <c r="C511">
         <v>0</v>
       </c>
@@ -28028,6 +29234,9 @@
       <c r="A512">
         <v>0</v>
       </c>
+      <c r="B512" t="s">
+        <v>346</v>
+      </c>
       <c r="C512">
         <v>0</v>
       </c>
@@ -28078,6 +29287,9 @@
       <c r="A513">
         <v>0</v>
       </c>
+      <c r="B513" t="s">
+        <v>347</v>
+      </c>
       <c r="C513">
         <v>0</v>
       </c>
@@ -28128,6 +29340,9 @@
       <c r="A514">
         <v>0</v>
       </c>
+      <c r="B514" t="s">
+        <v>348</v>
+      </c>
       <c r="C514">
         <v>0</v>
       </c>
@@ -28178,6 +29393,9 @@
       <c r="A515">
         <v>0</v>
       </c>
+      <c r="B515" t="s">
+        <v>349</v>
+      </c>
       <c r="C515">
         <v>0</v>
       </c>
@@ -28228,6 +29446,9 @@
       <c r="A516">
         <v>0</v>
       </c>
+      <c r="B516" t="s">
+        <v>350</v>
+      </c>
       <c r="C516">
         <v>0</v>
       </c>
@@ -28278,6 +29499,9 @@
       <c r="A517">
         <v>0</v>
       </c>
+      <c r="B517" t="s">
+        <v>351</v>
+      </c>
       <c r="C517">
         <v>0</v>
       </c>
@@ -28328,6 +29552,9 @@
       <c r="A518">
         <v>0</v>
       </c>
+      <c r="B518" t="s">
+        <v>352</v>
+      </c>
       <c r="C518">
         <v>0</v>
       </c>
@@ -28378,6 +29605,9 @@
       <c r="A519">
         <v>0</v>
       </c>
+      <c r="B519" t="s">
+        <v>353</v>
+      </c>
       <c r="C519">
         <v>0</v>
       </c>
@@ -28428,6 +29658,9 @@
       <c r="A520">
         <v>0</v>
       </c>
+      <c r="B520" t="s">
+        <v>354</v>
+      </c>
       <c r="C520">
         <v>0</v>
       </c>
@@ -28478,6 +29711,9 @@
       <c r="A521">
         <v>0</v>
       </c>
+      <c r="B521" t="s">
+        <v>355</v>
+      </c>
       <c r="C521">
         <v>0</v>
       </c>
@@ -28528,6 +29764,9 @@
       <c r="A522">
         <v>0</v>
       </c>
+      <c r="B522" t="s">
+        <v>356</v>
+      </c>
       <c r="C522">
         <v>0</v>
       </c>
@@ -28578,6 +29817,9 @@
       <c r="A523">
         <v>0</v>
       </c>
+      <c r="B523" t="s">
+        <v>357</v>
+      </c>
       <c r="C523">
         <v>0</v>
       </c>
@@ -28628,6 +29870,9 @@
       <c r="A524">
         <v>0</v>
       </c>
+      <c r="B524" t="s">
+        <v>358</v>
+      </c>
       <c r="C524">
         <v>0</v>
       </c>
@@ -28678,6 +29923,9 @@
       <c r="A525">
         <v>0</v>
       </c>
+      <c r="B525" t="s">
+        <v>359</v>
+      </c>
       <c r="C525">
         <v>0</v>
       </c>
@@ -28728,6 +29976,9 @@
       <c r="A526">
         <v>0</v>
       </c>
+      <c r="B526" t="s">
+        <v>360</v>
+      </c>
       <c r="C526">
         <v>0</v>
       </c>
@@ -28778,6 +30029,9 @@
       <c r="A527">
         <v>0</v>
       </c>
+      <c r="B527" t="s">
+        <v>361</v>
+      </c>
       <c r="C527">
         <v>0</v>
       </c>
@@ -28828,6 +30082,9 @@
       <c r="A528">
         <v>0</v>
       </c>
+      <c r="B528" t="s">
+        <v>362</v>
+      </c>
       <c r="C528">
         <v>0</v>
       </c>
@@ -28878,6 +30135,9 @@
       <c r="A529">
         <v>0</v>
       </c>
+      <c r="B529" t="s">
+        <v>363</v>
+      </c>
       <c r="C529">
         <v>0</v>
       </c>
@@ -28928,6 +30188,9 @@
       <c r="A530">
         <v>0</v>
       </c>
+      <c r="B530" t="s">
+        <v>364</v>
+      </c>
       <c r="C530">
         <v>0</v>
       </c>
@@ -28978,6 +30241,9 @@
       <c r="A531">
         <v>0</v>
       </c>
+      <c r="B531" t="s">
+        <v>365</v>
+      </c>
       <c r="C531">
         <v>0</v>
       </c>
@@ -29028,6 +30294,9 @@
       <c r="A532">
         <v>0</v>
       </c>
+      <c r="B532" t="s">
+        <v>366</v>
+      </c>
       <c r="C532">
         <v>0</v>
       </c>
@@ -29078,6 +30347,9 @@
       <c r="A533">
         <v>0</v>
       </c>
+      <c r="B533" t="s">
+        <v>367</v>
+      </c>
       <c r="C533">
         <v>0</v>
       </c>
@@ -29128,6 +30400,9 @@
       <c r="A534">
         <v>0</v>
       </c>
+      <c r="B534" t="s">
+        <v>368</v>
+      </c>
       <c r="C534">
         <v>0</v>
       </c>
@@ -29178,6 +30453,9 @@
       <c r="A535">
         <v>0</v>
       </c>
+      <c r="B535" t="s">
+        <v>369</v>
+      </c>
       <c r="C535">
         <v>0</v>
       </c>
@@ -29228,6 +30506,9 @@
       <c r="A536">
         <v>0</v>
       </c>
+      <c r="B536" t="s">
+        <v>370</v>
+      </c>
       <c r="C536">
         <v>0</v>
       </c>
@@ -29278,6 +30559,9 @@
       <c r="A537">
         <v>0</v>
       </c>
+      <c r="B537" t="s">
+        <v>371</v>
+      </c>
       <c r="C537">
         <v>0</v>
       </c>
@@ -29328,6 +30612,9 @@
       <c r="A538">
         <v>0</v>
       </c>
+      <c r="B538" t="s">
+        <v>372</v>
+      </c>
       <c r="C538">
         <v>0</v>
       </c>
@@ -29378,6 +30665,9 @@
       <c r="A539">
         <v>0</v>
       </c>
+      <c r="B539" t="s">
+        <v>373</v>
+      </c>
       <c r="C539">
         <v>0</v>
       </c>
@@ -29428,6 +30718,9 @@
       <c r="A540">
         <v>0</v>
       </c>
+      <c r="B540" t="s">
+        <v>374</v>
+      </c>
       <c r="C540">
         <v>0</v>
       </c>
@@ -29478,6 +30771,9 @@
       <c r="A541">
         <v>0</v>
       </c>
+      <c r="B541" t="s">
+        <v>375</v>
+      </c>
       <c r="C541">
         <v>0</v>
       </c>
@@ -29528,6 +30824,9 @@
       <c r="A542">
         <v>0</v>
       </c>
+      <c r="B542" t="s">
+        <v>376</v>
+      </c>
       <c r="C542">
         <v>0</v>
       </c>
@@ -29578,6 +30877,9 @@
       <c r="A543">
         <v>0</v>
       </c>
+      <c r="B543" t="s">
+        <v>377</v>
+      </c>
       <c r="C543">
         <v>0</v>
       </c>
@@ -29628,6 +30930,9 @@
       <c r="A544">
         <v>0</v>
       </c>
+      <c r="B544" t="s">
+        <v>378</v>
+      </c>
       <c r="C544">
         <v>0</v>
       </c>
@@ -29678,6 +30983,9 @@
       <c r="A545">
         <v>0</v>
       </c>
+      <c r="B545" t="s">
+        <v>379</v>
+      </c>
       <c r="C545">
         <v>0</v>
       </c>
@@ -29728,6 +31036,9 @@
       <c r="A546">
         <v>0</v>
       </c>
+      <c r="B546" t="s">
+        <v>380</v>
+      </c>
       <c r="C546">
         <v>0</v>
       </c>
@@ -29778,6 +31089,9 @@
       <c r="A547">
         <v>0</v>
       </c>
+      <c r="B547" t="s">
+        <v>381</v>
+      </c>
       <c r="C547">
         <v>0</v>
       </c>
@@ -29828,6 +31142,9 @@
       <c r="A548">
         <v>0</v>
       </c>
+      <c r="B548" t="s">
+        <v>382</v>
+      </c>
       <c r="C548">
         <v>0</v>
       </c>
@@ -29878,6 +31195,9 @@
       <c r="A549">
         <v>0</v>
       </c>
+      <c r="B549" t="s">
+        <v>383</v>
+      </c>
       <c r="C549">
         <v>0</v>
       </c>
@@ -29928,6 +31248,9 @@
       <c r="A550">
         <v>0</v>
       </c>
+      <c r="B550" t="s">
+        <v>384</v>
+      </c>
       <c r="C550">
         <v>0</v>
       </c>
@@ -29978,6 +31301,9 @@
       <c r="A551">
         <v>0</v>
       </c>
+      <c r="B551" t="s">
+        <v>385</v>
+      </c>
       <c r="C551">
         <v>0</v>
       </c>
@@ -30028,6 +31354,9 @@
       <c r="A552">
         <v>0</v>
       </c>
+      <c r="B552" t="s">
+        <v>386</v>
+      </c>
       <c r="C552">
         <v>0</v>
       </c>
@@ -30078,6 +31407,9 @@
       <c r="A553">
         <v>0</v>
       </c>
+      <c r="B553" t="s">
+        <v>387</v>
+      </c>
       <c r="C553">
         <v>0</v>
       </c>
@@ -30128,6 +31460,9 @@
       <c r="A554">
         <v>0</v>
       </c>
+      <c r="B554" t="s">
+        <v>388</v>
+      </c>
       <c r="C554">
         <v>0</v>
       </c>
@@ -30178,6 +31513,9 @@
       <c r="A555">
         <v>0</v>
       </c>
+      <c r="B555" t="s">
+        <v>389</v>
+      </c>
       <c r="C555">
         <v>0</v>
       </c>
@@ -30228,6 +31566,9 @@
       <c r="A556">
         <v>0</v>
       </c>
+      <c r="B556" t="s">
+        <v>390</v>
+      </c>
       <c r="C556">
         <v>0</v>
       </c>
@@ -30278,6 +31619,9 @@
       <c r="A557">
         <v>0</v>
       </c>
+      <c r="B557" t="s">
+        <v>391</v>
+      </c>
       <c r="C557">
         <v>0</v>
       </c>
@@ -30328,6 +31672,9 @@
       <c r="A558">
         <v>0</v>
       </c>
+      <c r="B558" t="s">
+        <v>392</v>
+      </c>
       <c r="C558">
         <v>0</v>
       </c>
@@ -30378,6 +31725,9 @@
       <c r="A559">
         <v>0</v>
       </c>
+      <c r="B559" t="s">
+        <v>393</v>
+      </c>
       <c r="C559">
         <v>0</v>
       </c>
@@ -30428,6 +31778,9 @@
       <c r="A560">
         <v>0</v>
       </c>
+      <c r="B560" t="s">
+        <v>394</v>
+      </c>
       <c r="C560">
         <v>0</v>
       </c>
@@ -30478,6 +31831,9 @@
       <c r="A561">
         <v>0</v>
       </c>
+      <c r="B561" t="s">
+        <v>395</v>
+      </c>
       <c r="C561">
         <v>0</v>
       </c>
@@ -30528,6 +31884,9 @@
       <c r="A562">
         <v>0</v>
       </c>
+      <c r="B562" t="s">
+        <v>396</v>
+      </c>
       <c r="C562">
         <v>0</v>
       </c>
@@ -30578,6 +31937,9 @@
       <c r="A563">
         <v>0</v>
       </c>
+      <c r="B563" t="s">
+        <v>397</v>
+      </c>
       <c r="C563">
         <v>0</v>
       </c>
@@ -30628,6 +31990,9 @@
       <c r="A564">
         <v>0</v>
       </c>
+      <c r="B564" t="s">
+        <v>398</v>
+      </c>
       <c r="C564">
         <v>0</v>
       </c>
@@ -30678,6 +32043,9 @@
       <c r="A565">
         <v>0</v>
       </c>
+      <c r="B565" t="s">
+        <v>399</v>
+      </c>
       <c r="C565">
         <v>0</v>
       </c>
@@ -30728,6 +32096,9 @@
       <c r="A566">
         <v>0</v>
       </c>
+      <c r="B566" t="s">
+        <v>400</v>
+      </c>
       <c r="C566">
         <v>0</v>
       </c>
@@ -30778,6 +32149,9 @@
       <c r="A567">
         <v>0</v>
       </c>
+      <c r="B567" t="s">
+        <v>401</v>
+      </c>
       <c r="C567">
         <v>0</v>
       </c>
@@ -30828,6 +32202,9 @@
       <c r="A568">
         <v>0</v>
       </c>
+      <c r="B568" t="s">
+        <v>402</v>
+      </c>
       <c r="C568">
         <v>0</v>
       </c>
@@ -30878,6 +32255,9 @@
       <c r="A569">
         <v>0</v>
       </c>
+      <c r="B569" t="s">
+        <v>403</v>
+      </c>
       <c r="C569">
         <v>0</v>
       </c>
@@ -30928,6 +32308,9 @@
       <c r="A570">
         <v>0</v>
       </c>
+      <c r="B570" t="s">
+        <v>404</v>
+      </c>
       <c r="C570">
         <v>0</v>
       </c>
@@ -30978,6 +32361,9 @@
       <c r="A571">
         <v>0</v>
       </c>
+      <c r="B571" t="s">
+        <v>405</v>
+      </c>
       <c r="C571">
         <v>0</v>
       </c>
@@ -31028,6 +32414,9 @@
       <c r="A572">
         <v>0</v>
       </c>
+      <c r="B572" t="s">
+        <v>406</v>
+      </c>
       <c r="C572">
         <v>0</v>
       </c>
@@ -31078,6 +32467,9 @@
       <c r="A573">
         <v>0</v>
       </c>
+      <c r="B573" t="s">
+        <v>407</v>
+      </c>
       <c r="C573">
         <v>0</v>
       </c>
@@ -31128,6 +32520,9 @@
       <c r="A574">
         <v>0</v>
       </c>
+      <c r="B574" t="s">
+        <v>408</v>
+      </c>
       <c r="C574">
         <v>0</v>
       </c>
@@ -31178,6 +32573,9 @@
       <c r="A575">
         <v>0</v>
       </c>
+      <c r="B575" t="s">
+        <v>409</v>
+      </c>
       <c r="C575">
         <v>0</v>
       </c>
@@ -31228,6 +32626,9 @@
       <c r="A576">
         <v>0</v>
       </c>
+      <c r="B576" t="s">
+        <v>410</v>
+      </c>
       <c r="C576">
         <v>0</v>
       </c>
@@ -31278,6 +32679,9 @@
       <c r="A577">
         <v>0</v>
       </c>
+      <c r="B577" t="s">
+        <v>411</v>
+      </c>
       <c r="C577">
         <v>0</v>
       </c>
@@ -31328,6 +32732,9 @@
       <c r="A578">
         <v>0</v>
       </c>
+      <c r="B578" t="s">
+        <v>412</v>
+      </c>
       <c r="C578">
         <v>0</v>
       </c>
@@ -31378,6 +32785,9 @@
       <c r="A579">
         <v>0</v>
       </c>
+      <c r="B579" t="s">
+        <v>413</v>
+      </c>
       <c r="C579">
         <v>0</v>
       </c>
@@ -31428,6 +32838,9 @@
       <c r="A580">
         <v>0</v>
       </c>
+      <c r="B580" t="s">
+        <v>414</v>
+      </c>
       <c r="C580">
         <v>0</v>
       </c>
@@ -31478,6 +32891,9 @@
       <c r="A581">
         <v>0</v>
       </c>
+      <c r="B581" t="s">
+        <v>415</v>
+      </c>
       <c r="C581">
         <v>0</v>
       </c>
@@ -31528,6 +32944,9 @@
       <c r="A582">
         <v>0</v>
       </c>
+      <c r="B582" t="s">
+        <v>416</v>
+      </c>
       <c r="C582">
         <v>0</v>
       </c>
@@ -31578,6 +32997,9 @@
       <c r="A583">
         <v>0</v>
       </c>
+      <c r="B583" t="s">
+        <v>417</v>
+      </c>
       <c r="C583">
         <v>0</v>
       </c>
@@ -31628,6 +33050,9 @@
       <c r="A584">
         <v>0</v>
       </c>
+      <c r="B584" t="s">
+        <v>418</v>
+      </c>
       <c r="C584">
         <v>0</v>
       </c>
@@ -31678,6 +33103,9 @@
       <c r="A585">
         <v>0</v>
       </c>
+      <c r="B585" t="s">
+        <v>419</v>
+      </c>
       <c r="C585">
         <v>0</v>
       </c>
@@ -31728,6 +33156,9 @@
       <c r="A586">
         <v>0</v>
       </c>
+      <c r="B586" t="s">
+        <v>420</v>
+      </c>
       <c r="C586">
         <v>0</v>
       </c>
@@ -31778,6 +33209,9 @@
       <c r="A587">
         <v>0</v>
       </c>
+      <c r="B587" t="s">
+        <v>421</v>
+      </c>
       <c r="C587">
         <v>0</v>
       </c>
@@ -31828,6 +33262,9 @@
       <c r="A588">
         <v>0</v>
       </c>
+      <c r="B588" t="s">
+        <v>422</v>
+      </c>
       <c r="C588">
         <v>0</v>
       </c>
@@ -31878,6 +33315,9 @@
       <c r="A589">
         <v>0</v>
       </c>
+      <c r="B589" t="s">
+        <v>423</v>
+      </c>
       <c r="C589">
         <v>0</v>
       </c>
@@ -31928,6 +33368,9 @@
       <c r="A590">
         <v>0</v>
       </c>
+      <c r="B590" t="s">
+        <v>424</v>
+      </c>
       <c r="C590">
         <v>0</v>
       </c>
@@ -31978,6 +33421,9 @@
       <c r="A591">
         <v>0</v>
       </c>
+      <c r="B591" t="s">
+        <v>425</v>
+      </c>
       <c r="C591">
         <v>0</v>
       </c>
@@ -32028,6 +33474,9 @@
       <c r="A592">
         <v>0</v>
       </c>
+      <c r="B592" t="s">
+        <v>426</v>
+      </c>
       <c r="C592">
         <v>0</v>
       </c>
@@ -32078,6 +33527,9 @@
       <c r="A593">
         <v>0</v>
       </c>
+      <c r="B593" t="s">
+        <v>427</v>
+      </c>
       <c r="C593">
         <v>0</v>
       </c>
@@ -32128,6 +33580,9 @@
       <c r="A594">
         <v>0</v>
       </c>
+      <c r="B594" t="s">
+        <v>428</v>
+      </c>
       <c r="C594">
         <v>0</v>
       </c>
@@ -32178,6 +33633,9 @@
       <c r="A595">
         <v>0</v>
       </c>
+      <c r="B595" t="s">
+        <v>429</v>
+      </c>
       <c r="C595">
         <v>0</v>
       </c>
@@ -32228,6 +33686,9 @@
       <c r="A596">
         <v>0</v>
       </c>
+      <c r="B596" t="s">
+        <v>430</v>
+      </c>
       <c r="C596">
         <v>0</v>
       </c>
@@ -32278,6 +33739,9 @@
       <c r="A597">
         <v>0</v>
       </c>
+      <c r="B597" t="s">
+        <v>431</v>
+      </c>
       <c r="C597">
         <v>0</v>
       </c>
@@ -32328,6 +33792,9 @@
       <c r="A598">
         <v>0</v>
       </c>
+      <c r="B598" t="s">
+        <v>432</v>
+      </c>
       <c r="C598">
         <v>0</v>
       </c>
@@ -32378,6 +33845,9 @@
       <c r="A599">
         <v>0</v>
       </c>
+      <c r="B599" t="s">
+        <v>433</v>
+      </c>
       <c r="C599">
         <v>0</v>
       </c>
@@ -32428,6 +33898,9 @@
       <c r="A600">
         <v>0</v>
       </c>
+      <c r="B600" t="s">
+        <v>434</v>
+      </c>
       <c r="C600">
         <v>0</v>
       </c>
@@ -32478,6 +33951,9 @@
       <c r="A601">
         <v>0</v>
       </c>
+      <c r="B601" t="s">
+        <v>435</v>
+      </c>
       <c r="C601">
         <v>0</v>
       </c>
@@ -32528,6 +34004,9 @@
       <c r="A602">
         <v>0</v>
       </c>
+      <c r="B602" t="s">
+        <v>436</v>
+      </c>
       <c r="C602">
         <v>0</v>
       </c>
@@ -32578,6 +34057,9 @@
       <c r="A603">
         <v>0</v>
       </c>
+      <c r="B603" t="s">
+        <v>437</v>
+      </c>
       <c r="C603">
         <v>0</v>
       </c>
@@ -32628,6 +34110,9 @@
       <c r="A604">
         <v>0</v>
       </c>
+      <c r="B604" t="s">
+        <v>438</v>
+      </c>
       <c r="C604">
         <v>0</v>
       </c>
@@ -32678,6 +34163,9 @@
       <c r="A605">
         <v>0</v>
       </c>
+      <c r="B605" t="s">
+        <v>439</v>
+      </c>
       <c r="C605">
         <v>0</v>
       </c>
@@ -32728,6 +34216,9 @@
       <c r="A606">
         <v>0</v>
       </c>
+      <c r="B606" t="s">
+        <v>440</v>
+      </c>
       <c r="C606">
         <v>0</v>
       </c>
@@ -32778,6 +34269,9 @@
       <c r="A607">
         <v>0</v>
       </c>
+      <c r="B607" t="s">
+        <v>441</v>
+      </c>
       <c r="C607">
         <v>0</v>
       </c>
@@ -32828,6 +34322,9 @@
       <c r="A608">
         <v>0</v>
       </c>
+      <c r="B608" t="s">
+        <v>442</v>
+      </c>
       <c r="C608">
         <v>0</v>
       </c>
@@ -32878,6 +34375,9 @@
       <c r="A609">
         <v>0</v>
       </c>
+      <c r="B609" t="s">
+        <v>443</v>
+      </c>
       <c r="C609">
         <v>0</v>
       </c>
@@ -32928,6 +34428,9 @@
       <c r="A610">
         <v>0</v>
       </c>
+      <c r="B610" t="s">
+        <v>444</v>
+      </c>
       <c r="C610">
         <v>0</v>
       </c>
@@ -32978,6 +34481,9 @@
       <c r="A611">
         <v>0</v>
       </c>
+      <c r="B611" t="s">
+        <v>445</v>
+      </c>
       <c r="C611">
         <v>0</v>
       </c>
@@ -33028,6 +34534,9 @@
       <c r="A612">
         <v>0</v>
       </c>
+      <c r="B612" t="s">
+        <v>446</v>
+      </c>
       <c r="C612">
         <v>0</v>
       </c>
@@ -33078,6 +34587,9 @@
       <c r="A613">
         <v>0</v>
       </c>
+      <c r="B613" t="s">
+        <v>447</v>
+      </c>
       <c r="C613">
         <v>0</v>
       </c>
@@ -33128,6 +34640,9 @@
       <c r="A614">
         <v>0</v>
       </c>
+      <c r="B614" t="s">
+        <v>448</v>
+      </c>
       <c r="C614">
         <v>0</v>
       </c>
@@ -33178,6 +34693,9 @@
       <c r="A615">
         <v>0</v>
       </c>
+      <c r="B615" t="s">
+        <v>449</v>
+      </c>
       <c r="C615">
         <v>0</v>
       </c>
@@ -33228,6 +34746,9 @@
       <c r="A616">
         <v>0</v>
       </c>
+      <c r="B616" t="s">
+        <v>450</v>
+      </c>
       <c r="C616">
         <v>0</v>
       </c>
@@ -33278,6 +34799,9 @@
       <c r="A617">
         <v>0</v>
       </c>
+      <c r="B617" t="s">
+        <v>451</v>
+      </c>
       <c r="C617">
         <v>0</v>
       </c>
@@ -33328,6 +34852,9 @@
       <c r="A618">
         <v>0</v>
       </c>
+      <c r="B618" t="s">
+        <v>452</v>
+      </c>
       <c r="C618">
         <v>0</v>
       </c>
@@ -33378,6 +34905,9 @@
       <c r="A619">
         <v>0</v>
       </c>
+      <c r="B619" t="s">
+        <v>453</v>
+      </c>
       <c r="C619">
         <v>0</v>
       </c>
@@ -33428,6 +34958,9 @@
       <c r="A620">
         <v>0</v>
       </c>
+      <c r="B620" t="s">
+        <v>454</v>
+      </c>
       <c r="C620">
         <v>0</v>
       </c>
@@ -33478,6 +35011,9 @@
       <c r="A621">
         <v>0</v>
       </c>
+      <c r="B621" t="s">
+        <v>455</v>
+      </c>
       <c r="C621">
         <v>0</v>
       </c>
@@ -33528,6 +35064,9 @@
       <c r="A622">
         <v>0</v>
       </c>
+      <c r="B622" t="s">
+        <v>456</v>
+      </c>
       <c r="C622">
         <v>0</v>
       </c>
@@ -33578,6 +35117,9 @@
       <c r="A623">
         <v>0</v>
       </c>
+      <c r="B623" t="s">
+        <v>457</v>
+      </c>
       <c r="C623">
         <v>0</v>
       </c>
@@ -33628,6 +35170,9 @@
       <c r="A624">
         <v>0</v>
       </c>
+      <c r="B624" t="s">
+        <v>458</v>
+      </c>
       <c r="C624">
         <v>0</v>
       </c>
@@ -33678,6 +35223,9 @@
       <c r="A625">
         <v>0</v>
       </c>
+      <c r="B625" t="s">
+        <v>459</v>
+      </c>
       <c r="C625">
         <v>0</v>
       </c>
@@ -33728,6 +35276,9 @@
       <c r="A626">
         <v>0</v>
       </c>
+      <c r="B626" t="s">
+        <v>460</v>
+      </c>
       <c r="C626">
         <v>0</v>
       </c>
@@ -33778,6 +35329,9 @@
       <c r="A627">
         <v>0</v>
       </c>
+      <c r="B627" t="s">
+        <v>461</v>
+      </c>
       <c r="C627">
         <v>0</v>
       </c>
@@ -33828,6 +35382,9 @@
       <c r="A628">
         <v>0</v>
       </c>
+      <c r="B628" t="s">
+        <v>462</v>
+      </c>
       <c r="C628">
         <v>0</v>
       </c>
@@ -33878,6 +35435,9 @@
       <c r="A629">
         <v>0</v>
       </c>
+      <c r="B629" t="s">
+        <v>463</v>
+      </c>
       <c r="C629">
         <v>0</v>
       </c>
@@ -33928,6 +35488,9 @@
       <c r="A630">
         <v>0</v>
       </c>
+      <c r="B630" t="s">
+        <v>464</v>
+      </c>
       <c r="C630">
         <v>0</v>
       </c>
@@ -33978,6 +35541,9 @@
       <c r="A631">
         <v>0</v>
       </c>
+      <c r="B631" t="s">
+        <v>465</v>
+      </c>
       <c r="C631">
         <v>0</v>
       </c>
@@ -34028,6 +35594,9 @@
       <c r="A632">
         <v>0</v>
       </c>
+      <c r="B632" t="s">
+        <v>466</v>
+      </c>
       <c r="C632">
         <v>0</v>
       </c>
@@ -34078,6 +35647,9 @@
       <c r="A633">
         <v>0</v>
       </c>
+      <c r="B633" t="s">
+        <v>467</v>
+      </c>
       <c r="C633">
         <v>0</v>
       </c>
@@ -34128,6 +35700,9 @@
       <c r="A634">
         <v>0</v>
       </c>
+      <c r="B634" t="s">
+        <v>468</v>
+      </c>
       <c r="C634">
         <v>0</v>
       </c>
@@ -34178,6 +35753,9 @@
       <c r="A635">
         <v>0</v>
       </c>
+      <c r="B635" t="s">
+        <v>469</v>
+      </c>
       <c r="C635">
         <v>0</v>
       </c>
@@ -34228,6 +35806,9 @@
       <c r="A636">
         <v>0</v>
       </c>
+      <c r="B636" t="s">
+        <v>470</v>
+      </c>
       <c r="C636">
         <v>0</v>
       </c>
@@ -34278,6 +35859,9 @@
       <c r="A637">
         <v>0</v>
       </c>
+      <c r="B637" t="s">
+        <v>471</v>
+      </c>
       <c r="C637">
         <v>0</v>
       </c>
@@ -34328,6 +35912,9 @@
       <c r="A638">
         <v>0</v>
       </c>
+      <c r="B638" t="s">
+        <v>472</v>
+      </c>
       <c r="C638">
         <v>0</v>
       </c>
@@ -34378,6 +35965,9 @@
       <c r="A639">
         <v>0</v>
       </c>
+      <c r="B639" t="s">
+        <v>473</v>
+      </c>
       <c r="C639">
         <v>0</v>
       </c>
@@ -34428,6 +36018,9 @@
       <c r="A640">
         <v>0</v>
       </c>
+      <c r="B640" t="s">
+        <v>474</v>
+      </c>
       <c r="C640">
         <v>0</v>
       </c>
@@ -34478,6 +36071,9 @@
       <c r="A641">
         <v>0</v>
       </c>
+      <c r="B641" t="s">
+        <v>475</v>
+      </c>
       <c r="C641">
         <v>0</v>
       </c>
@@ -34528,6 +36124,9 @@
       <c r="A642">
         <v>0</v>
       </c>
+      <c r="B642" t="s">
+        <v>476</v>
+      </c>
       <c r="C642">
         <v>0</v>
       </c>
@@ -34578,6 +36177,9 @@
       <c r="A643">
         <v>0</v>
       </c>
+      <c r="B643" t="s">
+        <v>477</v>
+      </c>
       <c r="C643">
         <v>0</v>
       </c>
@@ -34628,6 +36230,9 @@
       <c r="A644">
         <v>0</v>
       </c>
+      <c r="B644" t="s">
+        <v>478</v>
+      </c>
       <c r="C644">
         <v>0</v>
       </c>
@@ -34678,6 +36283,9 @@
       <c r="A645">
         <v>0</v>
       </c>
+      <c r="B645" t="s">
+        <v>479</v>
+      </c>
       <c r="C645">
         <v>0</v>
       </c>
@@ -34728,6 +36336,9 @@
       <c r="A646">
         <v>0</v>
       </c>
+      <c r="B646" t="s">
+        <v>480</v>
+      </c>
       <c r="C646">
         <v>0</v>
       </c>
@@ -34778,6 +36389,9 @@
       <c r="A647">
         <v>0</v>
       </c>
+      <c r="B647" t="s">
+        <v>481</v>
+      </c>
       <c r="C647">
         <v>0</v>
       </c>
@@ -34828,6 +36442,9 @@
       <c r="A648">
         <v>0</v>
       </c>
+      <c r="B648" t="s">
+        <v>482</v>
+      </c>
       <c r="C648">
         <v>0</v>
       </c>
@@ -34878,6 +36495,9 @@
       <c r="A649">
         <v>0</v>
       </c>
+      <c r="B649" t="s">
+        <v>483</v>
+      </c>
       <c r="C649">
         <v>0</v>
       </c>
@@ -34928,6 +36548,9 @@
       <c r="A650">
         <v>0</v>
       </c>
+      <c r="B650" t="s">
+        <v>484</v>
+      </c>
       <c r="C650">
         <v>0</v>
       </c>
@@ -34978,6 +36601,9 @@
       <c r="A651">
         <v>0</v>
       </c>
+      <c r="B651" t="s">
+        <v>485</v>
+      </c>
       <c r="C651">
         <v>0</v>
       </c>
@@ -35028,6 +36654,9 @@
       <c r="A652">
         <v>0</v>
       </c>
+      <c r="B652" t="s">
+        <v>486</v>
+      </c>
       <c r="C652">
         <v>0</v>
       </c>
@@ -35078,6 +36707,9 @@
       <c r="A653">
         <v>0</v>
       </c>
+      <c r="B653" t="s">
+        <v>487</v>
+      </c>
       <c r="C653">
         <v>0</v>
       </c>
@@ -35128,6 +36760,9 @@
       <c r="A654">
         <v>0</v>
       </c>
+      <c r="B654" t="s">
+        <v>488</v>
+      </c>
       <c r="C654">
         <v>0</v>
       </c>
@@ -35178,6 +36813,9 @@
       <c r="A655">
         <v>0</v>
       </c>
+      <c r="B655" t="s">
+        <v>489</v>
+      </c>
       <c r="C655">
         <v>0</v>
       </c>
@@ -35228,6 +36866,9 @@
       <c r="A656">
         <v>0</v>
       </c>
+      <c r="B656" t="s">
+        <v>490</v>
+      </c>
       <c r="C656">
         <v>0</v>
       </c>
@@ -35278,6 +36919,9 @@
       <c r="A657">
         <v>0</v>
       </c>
+      <c r="B657" t="s">
+        <v>491</v>
+      </c>
       <c r="C657">
         <v>0</v>
       </c>
@@ -35328,6 +36972,9 @@
       <c r="A658">
         <v>0</v>
       </c>
+      <c r="B658" t="s">
+        <v>492</v>
+      </c>
       <c r="C658">
         <v>0</v>
       </c>
@@ -35378,6 +37025,9 @@
       <c r="A659">
         <v>0</v>
       </c>
+      <c r="B659" t="s">
+        <v>493</v>
+      </c>
       <c r="C659">
         <v>0</v>
       </c>
@@ -35428,6 +37078,9 @@
       <c r="A660">
         <v>0</v>
       </c>
+      <c r="B660" t="s">
+        <v>494</v>
+      </c>
       <c r="C660">
         <v>0</v>
       </c>
@@ -35478,6 +37131,9 @@
       <c r="A661">
         <v>0</v>
       </c>
+      <c r="B661" t="s">
+        <v>495</v>
+      </c>
       <c r="C661">
         <v>0</v>
       </c>
@@ -35528,6 +37184,9 @@
       <c r="A662">
         <v>0</v>
       </c>
+      <c r="B662" t="s">
+        <v>496</v>
+      </c>
       <c r="C662">
         <v>0</v>
       </c>
@@ -35578,6 +37237,9 @@
       <c r="A663">
         <v>0</v>
       </c>
+      <c r="B663" t="s">
+        <v>497</v>
+      </c>
       <c r="C663">
         <v>0</v>
       </c>
@@ -35628,6 +37290,9 @@
       <c r="A664">
         <v>0</v>
       </c>
+      <c r="B664" t="s">
+        <v>498</v>
+      </c>
       <c r="C664">
         <v>0</v>
       </c>
@@ -35678,6 +37343,9 @@
       <c r="A665">
         <v>0</v>
       </c>
+      <c r="B665" t="s">
+        <v>499</v>
+      </c>
       <c r="C665">
         <v>0</v>
       </c>
@@ -35728,6 +37396,9 @@
       <c r="A666">
         <v>0</v>
       </c>
+      <c r="B666" t="s">
+        <v>500</v>
+      </c>
       <c r="C666">
         <v>0</v>
       </c>
@@ -35778,6 +37449,9 @@
       <c r="A667">
         <v>0</v>
       </c>
+      <c r="B667" t="s">
+        <v>501</v>
+      </c>
       <c r="C667">
         <v>0</v>
       </c>
@@ -35828,6 +37502,9 @@
       <c r="A668">
         <v>0</v>
       </c>
+      <c r="B668" t="s">
+        <v>502</v>
+      </c>
       <c r="C668">
         <v>0</v>
       </c>
@@ -35878,6 +37555,9 @@
       <c r="A669">
         <v>0</v>
       </c>
+      <c r="B669" t="s">
+        <v>503</v>
+      </c>
       <c r="C669">
         <v>0</v>
       </c>
@@ -35928,6 +37608,9 @@
       <c r="A670">
         <v>0</v>
       </c>
+      <c r="B670" t="s">
+        <v>504</v>
+      </c>
       <c r="C670">
         <v>0</v>
       </c>
@@ -35978,6 +37661,9 @@
       <c r="A671">
         <v>0</v>
       </c>
+      <c r="B671" t="s">
+        <v>505</v>
+      </c>
       <c r="C671">
         <v>0</v>
       </c>
@@ -36028,6 +37714,9 @@
       <c r="A672">
         <v>0</v>
       </c>
+      <c r="B672" t="s">
+        <v>506</v>
+      </c>
       <c r="C672">
         <v>0</v>
       </c>
@@ -36078,6 +37767,9 @@
       <c r="A673">
         <v>0</v>
       </c>
+      <c r="B673" t="s">
+        <v>507</v>
+      </c>
       <c r="C673">
         <v>0</v>
       </c>
@@ -36128,6 +37820,9 @@
       <c r="A674">
         <v>0</v>
       </c>
+      <c r="B674" t="s">
+        <v>508</v>
+      </c>
       <c r="C674">
         <v>0</v>
       </c>
@@ -36178,6 +37873,9 @@
       <c r="A675">
         <v>0</v>
       </c>
+      <c r="B675" t="s">
+        <v>509</v>
+      </c>
       <c r="C675">
         <v>0</v>
       </c>
@@ -36228,6 +37926,9 @@
       <c r="A676">
         <v>0</v>
       </c>
+      <c r="B676" t="s">
+        <v>510</v>
+      </c>
       <c r="C676">
         <v>0</v>
       </c>
@@ -36278,6 +37979,9 @@
       <c r="A677">
         <v>0</v>
       </c>
+      <c r="B677" t="s">
+        <v>511</v>
+      </c>
       <c r="C677">
         <v>0</v>
       </c>
@@ -36328,6 +38032,9 @@
       <c r="A678">
         <v>0</v>
       </c>
+      <c r="B678" t="s">
+        <v>512</v>
+      </c>
       <c r="C678">
         <v>0</v>
       </c>
@@ -36378,6 +38085,9 @@
       <c r="A679">
         <v>0</v>
       </c>
+      <c r="B679" t="s">
+        <v>513</v>
+      </c>
       <c r="C679">
         <v>0</v>
       </c>
@@ -36428,6 +38138,9 @@
       <c r="A680">
         <v>0</v>
       </c>
+      <c r="B680" t="s">
+        <v>514</v>
+      </c>
       <c r="C680">
         <v>0</v>
       </c>
@@ -36478,6 +38191,9 @@
       <c r="A681">
         <v>0</v>
       </c>
+      <c r="B681" t="s">
+        <v>515</v>
+      </c>
       <c r="C681">
         <v>0</v>
       </c>
@@ -36528,6 +38244,9 @@
       <c r="A682">
         <v>0</v>
       </c>
+      <c r="B682" t="s">
+        <v>516</v>
+      </c>
       <c r="C682">
         <v>0</v>
       </c>
@@ -36578,6 +38297,9 @@
       <c r="A683">
         <v>0</v>
       </c>
+      <c r="B683" t="s">
+        <v>517</v>
+      </c>
       <c r="C683">
         <v>0</v>
       </c>
@@ -36628,6 +38350,9 @@
       <c r="A684">
         <v>0</v>
       </c>
+      <c r="B684" t="s">
+        <v>518</v>
+      </c>
       <c r="C684">
         <v>0</v>
       </c>
@@ -36678,6 +38403,9 @@
       <c r="A685">
         <v>0</v>
       </c>
+      <c r="B685" t="s">
+        <v>519</v>
+      </c>
       <c r="C685">
         <v>0</v>
       </c>
@@ -36728,6 +38456,9 @@
       <c r="A686">
         <v>0</v>
       </c>
+      <c r="B686" t="s">
+        <v>520</v>
+      </c>
       <c r="C686">
         <v>0</v>
       </c>
@@ -36778,6 +38509,9 @@
       <c r="A687">
         <v>0</v>
       </c>
+      <c r="B687" t="s">
+        <v>521</v>
+      </c>
       <c r="C687">
         <v>0</v>
       </c>
@@ -36828,6 +38562,9 @@
       <c r="A688">
         <v>0</v>
       </c>
+      <c r="B688" t="s">
+        <v>522</v>
+      </c>
       <c r="C688">
         <v>0</v>
       </c>
@@ -36878,6 +38615,9 @@
       <c r="A689">
         <v>0</v>
       </c>
+      <c r="B689" t="s">
+        <v>523</v>
+      </c>
       <c r="C689">
         <v>0</v>
       </c>
@@ -36928,6 +38668,9 @@
       <c r="A690">
         <v>0</v>
       </c>
+      <c r="B690" t="s">
+        <v>524</v>
+      </c>
       <c r="C690">
         <v>0</v>
       </c>
@@ -36978,6 +38721,9 @@
       <c r="A691">
         <v>0</v>
       </c>
+      <c r="B691" t="s">
+        <v>525</v>
+      </c>
       <c r="C691">
         <v>0</v>
       </c>
@@ -37028,6 +38774,9 @@
       <c r="A692">
         <v>0</v>
       </c>
+      <c r="B692" t="s">
+        <v>526</v>
+      </c>
       <c r="C692">
         <v>0</v>
       </c>
@@ -37078,6 +38827,9 @@
       <c r="A693">
         <v>0</v>
       </c>
+      <c r="B693" t="s">
+        <v>527</v>
+      </c>
       <c r="C693">
         <v>0</v>
       </c>
@@ -37128,6 +38880,9 @@
       <c r="A694">
         <v>0</v>
       </c>
+      <c r="B694" t="s">
+        <v>528</v>
+      </c>
       <c r="C694">
         <v>0</v>
       </c>
@@ -37178,6 +38933,9 @@
       <c r="A695">
         <v>0</v>
       </c>
+      <c r="B695" t="s">
+        <v>529</v>
+      </c>
       <c r="C695">
         <v>0</v>
       </c>
@@ -37228,6 +38986,9 @@
       <c r="A696">
         <v>0</v>
       </c>
+      <c r="B696" t="s">
+        <v>530</v>
+      </c>
       <c r="C696">
         <v>0</v>
       </c>
@@ -37278,6 +39039,9 @@
       <c r="A697">
         <v>0</v>
       </c>
+      <c r="B697" t="s">
+        <v>531</v>
+      </c>
       <c r="C697">
         <v>0</v>
       </c>
@@ -37328,6 +39092,9 @@
       <c r="A698">
         <v>0</v>
       </c>
+      <c r="B698" t="s">
+        <v>532</v>
+      </c>
       <c r="C698">
         <v>0</v>
       </c>
@@ -37378,6 +39145,9 @@
       <c r="A699">
         <v>0</v>
       </c>
+      <c r="B699" t="s">
+        <v>533</v>
+      </c>
       <c r="C699">
         <v>0</v>
       </c>
@@ -37428,6 +39198,9 @@
       <c r="A700">
         <v>0</v>
       </c>
+      <c r="B700" t="s">
+        <v>534</v>
+      </c>
       <c r="C700">
         <v>0</v>
       </c>
@@ -37478,6 +39251,9 @@
       <c r="A701">
         <v>0</v>
       </c>
+      <c r="B701" t="s">
+        <v>535</v>
+      </c>
       <c r="C701">
         <v>0</v>
       </c>
@@ -37528,6 +39304,9 @@
       <c r="A702">
         <v>0</v>
       </c>
+      <c r="B702" t="s">
+        <v>536</v>
+      </c>
       <c r="C702">
         <v>0</v>
       </c>
@@ -37578,6 +39357,9 @@
       <c r="A703">
         <v>0</v>
       </c>
+      <c r="B703" t="s">
+        <v>537</v>
+      </c>
       <c r="C703">
         <v>0</v>
       </c>
@@ -37628,6 +39410,9 @@
       <c r="A704">
         <v>0</v>
       </c>
+      <c r="B704" t="s">
+        <v>538</v>
+      </c>
       <c r="C704">
         <v>0</v>
       </c>
@@ -37678,6 +39463,9 @@
       <c r="A705">
         <v>0</v>
       </c>
+      <c r="B705" t="s">
+        <v>539</v>
+      </c>
       <c r="C705">
         <v>0</v>
       </c>
@@ -37728,6 +39516,9 @@
       <c r="A706">
         <v>0</v>
       </c>
+      <c r="B706" t="s">
+        <v>540</v>
+      </c>
       <c r="C706">
         <v>0</v>
       </c>
@@ -37778,6 +39569,9 @@
       <c r="A707">
         <v>0</v>
       </c>
+      <c r="B707" t="s">
+        <v>541</v>
+      </c>
       <c r="C707">
         <v>0</v>
       </c>
@@ -37828,6 +39622,9 @@
       <c r="A708">
         <v>0</v>
       </c>
+      <c r="B708" t="s">
+        <v>542</v>
+      </c>
       <c r="C708">
         <v>0</v>
       </c>
@@ -37878,6 +39675,9 @@
       <c r="A709">
         <v>0</v>
       </c>
+      <c r="B709" t="s">
+        <v>543</v>
+      </c>
       <c r="C709">
         <v>0</v>
       </c>
@@ -37928,6 +39728,9 @@
       <c r="A710">
         <v>0</v>
       </c>
+      <c r="B710" t="s">
+        <v>544</v>
+      </c>
       <c r="C710">
         <v>0</v>
       </c>
@@ -37978,6 +39781,9 @@
       <c r="A711">
         <v>0</v>
       </c>
+      <c r="B711" t="s">
+        <v>545</v>
+      </c>
       <c r="C711">
         <v>0</v>
       </c>
@@ -38028,6 +39834,9 @@
       <c r="A712">
         <v>0</v>
       </c>
+      <c r="B712" t="s">
+        <v>546</v>
+      </c>
       <c r="C712">
         <v>0</v>
       </c>
@@ -38078,6 +39887,9 @@
       <c r="A713">
         <v>0</v>
       </c>
+      <c r="B713" t="s">
+        <v>547</v>
+      </c>
       <c r="C713">
         <v>0</v>
       </c>
@@ -38128,6 +39940,9 @@
       <c r="A714">
         <v>0</v>
       </c>
+      <c r="B714" t="s">
+        <v>548</v>
+      </c>
       <c r="C714">
         <v>0</v>
       </c>
@@ -38178,6 +39993,9 @@
       <c r="A715">
         <v>0</v>
       </c>
+      <c r="B715" t="s">
+        <v>549</v>
+      </c>
       <c r="C715">
         <v>0</v>
       </c>
@@ -38228,6 +40046,9 @@
       <c r="A716">
         <v>0</v>
       </c>
+      <c r="B716" t="s">
+        <v>550</v>
+      </c>
       <c r="C716">
         <v>0</v>
       </c>
@@ -38278,6 +40099,9 @@
       <c r="A717">
         <v>0</v>
       </c>
+      <c r="B717" t="s">
+        <v>551</v>
+      </c>
       <c r="C717">
         <v>0</v>
       </c>
@@ -38328,6 +40152,9 @@
       <c r="A718">
         <v>0</v>
       </c>
+      <c r="B718" t="s">
+        <v>552</v>
+      </c>
       <c r="C718">
         <v>0</v>
       </c>
@@ -38378,6 +40205,9 @@
       <c r="A719">
         <v>0</v>
       </c>
+      <c r="B719" t="s">
+        <v>553</v>
+      </c>
       <c r="C719">
         <v>0</v>
       </c>
@@ -38428,6 +40258,9 @@
       <c r="A720">
         <v>0</v>
       </c>
+      <c r="B720" t="s">
+        <v>554</v>
+      </c>
       <c r="C720">
         <v>0</v>
       </c>
@@ -38478,6 +40311,9 @@
       <c r="A721">
         <v>0</v>
       </c>
+      <c r="B721" t="s">
+        <v>555</v>
+      </c>
       <c r="C721">
         <v>0</v>
       </c>
@@ -38528,6 +40364,9 @@
       <c r="A722">
         <v>0</v>
       </c>
+      <c r="B722" t="s">
+        <v>556</v>
+      </c>
       <c r="C722">
         <v>0</v>
       </c>
@@ -38578,6 +40417,9 @@
       <c r="A723">
         <v>0</v>
       </c>
+      <c r="B723" t="s">
+        <v>557</v>
+      </c>
       <c r="C723">
         <v>0</v>
       </c>
@@ -38628,6 +40470,9 @@
       <c r="A724">
         <v>0</v>
       </c>
+      <c r="B724" t="s">
+        <v>558</v>
+      </c>
       <c r="C724">
         <v>0</v>
       </c>
@@ -38678,6 +40523,9 @@
       <c r="A725">
         <v>0</v>
       </c>
+      <c r="B725" t="s">
+        <v>559</v>
+      </c>
       <c r="C725">
         <v>0</v>
       </c>
@@ -38728,6 +40576,9 @@
       <c r="A726">
         <v>0</v>
       </c>
+      <c r="B726" t="s">
+        <v>560</v>
+      </c>
       <c r="C726">
         <v>0</v>
       </c>
@@ -38778,6 +40629,9 @@
       <c r="A727">
         <v>0</v>
       </c>
+      <c r="B727" t="s">
+        <v>561</v>
+      </c>
       <c r="C727">
         <v>0</v>
       </c>
@@ -38828,6 +40682,9 @@
       <c r="A728">
         <v>0</v>
       </c>
+      <c r="B728" t="s">
+        <v>562</v>
+      </c>
       <c r="C728">
         <v>0</v>
       </c>
@@ -38878,6 +40735,9 @@
       <c r="A729">
         <v>0</v>
       </c>
+      <c r="B729" t="s">
+        <v>563</v>
+      </c>
       <c r="C729">
         <v>0</v>
       </c>
@@ -38928,6 +40788,9 @@
       <c r="A730">
         <v>0</v>
       </c>
+      <c r="B730" t="s">
+        <v>564</v>
+      </c>
       <c r="C730">
         <v>0</v>
       </c>
@@ -38978,6 +40841,9 @@
       <c r="A731">
         <v>0</v>
       </c>
+      <c r="B731" t="s">
+        <v>565</v>
+      </c>
       <c r="C731">
         <v>0</v>
       </c>
@@ -39028,6 +40894,9 @@
       <c r="A732">
         <v>0</v>
       </c>
+      <c r="B732" t="s">
+        <v>566</v>
+      </c>
       <c r="C732">
         <v>0</v>
       </c>
@@ -39078,6 +40947,9 @@
       <c r="A733">
         <v>0</v>
       </c>
+      <c r="B733" t="s">
+        <v>567</v>
+      </c>
       <c r="C733">
         <v>0</v>
       </c>
@@ -39128,6 +41000,9 @@
       <c r="A734">
         <v>0</v>
       </c>
+      <c r="B734" t="s">
+        <v>568</v>
+      </c>
       <c r="C734">
         <v>0</v>
       </c>
@@ -39178,6 +41053,9 @@
       <c r="A735">
         <v>0</v>
       </c>
+      <c r="B735" t="s">
+        <v>569</v>
+      </c>
       <c r="C735">
         <v>0</v>
       </c>
@@ -39228,6 +41106,9 @@
       <c r="A736">
         <v>0</v>
       </c>
+      <c r="B736" t="s">
+        <v>570</v>
+      </c>
       <c r="C736">
         <v>0</v>
       </c>
@@ -39278,6 +41159,9 @@
       <c r="A737">
         <v>0</v>
       </c>
+      <c r="B737" t="s">
+        <v>571</v>
+      </c>
       <c r="C737">
         <v>0</v>
       </c>
@@ -39328,6 +41212,9 @@
       <c r="A738">
         <v>0</v>
       </c>
+      <c r="B738" t="s">
+        <v>572</v>
+      </c>
       <c r="C738">
         <v>0</v>
       </c>
@@ -39378,6 +41265,9 @@
       <c r="A739">
         <v>0</v>
       </c>
+      <c r="B739" t="s">
+        <v>573</v>
+      </c>
       <c r="C739">
         <v>0</v>
       </c>
@@ -39428,6 +41318,9 @@
       <c r="A740">
         <v>0</v>
       </c>
+      <c r="B740" t="s">
+        <v>574</v>
+      </c>
       <c r="C740">
         <v>0</v>
       </c>
@@ -39478,6 +41371,9 @@
       <c r="A741">
         <v>0</v>
       </c>
+      <c r="B741" t="s">
+        <v>575</v>
+      </c>
       <c r="C741">
         <v>0</v>
       </c>
@@ -39528,6 +41424,9 @@
       <c r="A742">
         <v>0</v>
       </c>
+      <c r="B742" t="s">
+        <v>576</v>
+      </c>
       <c r="C742">
         <v>0</v>
       </c>
@@ -39578,6 +41477,9 @@
       <c r="A743">
         <v>0</v>
       </c>
+      <c r="B743" t="s">
+        <v>577</v>
+      </c>
       <c r="C743">
         <v>0</v>
       </c>
@@ -39628,6 +41530,9 @@
       <c r="A744">
         <v>0</v>
       </c>
+      <c r="B744" t="s">
+        <v>578</v>
+      </c>
       <c r="C744">
         <v>0</v>
       </c>
@@ -39678,6 +41583,9 @@
       <c r="A745">
         <v>0</v>
       </c>
+      <c r="B745" t="s">
+        <v>579</v>
+      </c>
       <c r="C745">
         <v>0</v>
       </c>
@@ -39728,6 +41636,9 @@
       <c r="A746">
         <v>0</v>
       </c>
+      <c r="B746" t="s">
+        <v>580</v>
+      </c>
       <c r="C746">
         <v>0</v>
       </c>
@@ -39778,6 +41689,9 @@
       <c r="A747">
         <v>0</v>
       </c>
+      <c r="B747" t="s">
+        <v>581</v>
+      </c>
       <c r="C747">
         <v>0</v>
       </c>
@@ -39828,6 +41742,9 @@
       <c r="A748">
         <v>0</v>
       </c>
+      <c r="B748" t="s">
+        <v>582</v>
+      </c>
       <c r="C748">
         <v>0</v>
       </c>
@@ -39878,6 +41795,9 @@
       <c r="A749">
         <v>0</v>
       </c>
+      <c r="B749" t="s">
+        <v>583</v>
+      </c>
       <c r="C749">
         <v>0</v>
       </c>
@@ -39928,6 +41848,9 @@
       <c r="A750">
         <v>0</v>
       </c>
+      <c r="B750" t="s">
+        <v>584</v>
+      </c>
       <c r="C750">
         <v>0</v>
       </c>
@@ -39978,6 +41901,9 @@
       <c r="A751">
         <v>0</v>
       </c>
+      <c r="B751" t="s">
+        <v>585</v>
+      </c>
       <c r="C751">
         <v>0</v>
       </c>
@@ -40028,6 +41954,9 @@
       <c r="A752">
         <v>0</v>
       </c>
+      <c r="B752" t="s">
+        <v>586</v>
+      </c>
       <c r="C752">
         <v>0</v>
       </c>
@@ -40077,6 +42006,9 @@
     <row r="753" spans="1:17">
       <c r="A753">
         <v>0</v>
+      </c>
+      <c r="B753" t="s">
+        <v>587</v>
       </c>
       <c r="C753">
         <v>0</v>
@@ -40128,6 +42060,9 @@
       <c r="A754">
         <v>133687</v>
       </c>
+      <c r="B754" t="s">
+        <v>588</v>
+      </c>
       <c r="C754">
         <v>102373</v>
       </c>
@@ -40179,7 +42114,7 @@
         <v>140</v>
       </c>
       <c r="B755" t="s">
-        <v>267</v>
+        <v>589</v>
       </c>
       <c r="C755">
         <v>393</v>
@@ -40230,6 +42165,9 @@
     <row r="756" spans="1:17">
       <c r="A756">
         <v>133827</v>
+      </c>
+      <c r="B756" t="s">
+        <v>590</v>
       </c>
       <c r="C756">
         <v>102766</v>
